--- a/Flow_Pressure_Dashboard.xlsx
+++ b/Flow_Pressure_Dashboard.xlsx
@@ -27,7 +27,7 @@
     <numFmt numFmtId="166" formatCode="0.000000"/>
     <numFmt numFmtId="167" formatCode="0.000"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -46,14 +46,9 @@
       <sz val="9"/>
     </font>
     <font>
-      <i val="1"/>
-      <color rgb="002E75B6"/>
-      <sz val="9"/>
-    </font>
-    <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="15"/>
+      <sz val="14"/>
     </font>
     <font>
       <b val="1"/>
@@ -66,27 +61,24 @@
       <sz val="11"/>
     </font>
     <font>
-      <i val="1"/>
-      <color rgb="00C55A11"/>
-      <sz val="9"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="11"/>
     </font>
     <font>
-      <i val="1"/>
-      <color rgb="0070AD47"/>
-      <sz val="9"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C55A11"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="9"/>
-    </font>
-    <font>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="14"/>
     </font>
     <font>
       <b val="1"/>
@@ -98,13 +90,13 @@
       <sz val="10"/>
     </font>
     <font>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
       <i val="1"/>
       <color rgb="00595959"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="00000000"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="14">
@@ -126,7 +118,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C55A11"/>
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -136,12 +133,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00C55A11"/>
       </patternFill>
     </fill>
     <fill>
@@ -175,7 +167,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -195,11 +187,32 @@
       <top style="medium"/>
       <bottom style="medium"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -216,49 +229,45 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="6" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -281,49 +290,66 @@
     <xf numFmtId="167" fontId="0" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="4"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="001F4E79"/>
+        <sz val="10"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00BDD7EE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00C55A11"/>
+        <sz val="10"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -423,11 +449,11 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Dashboard'!D14</f>
+              <f>'Dashboard'!C24</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="18000">
+            <a:ln w="20000">
               <a:solidFill>
                 <a:srgbClr val="2E75B6"/>
               </a:solidFill>
@@ -444,12 +470,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Dashboard'!$A$15:$A$114</f>
+              <f>'Dashboard'!$A$25:$A$124</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$D$15:$D$114</f>
+              <f>'Dashboard'!$C$25:$C$124</f>
             </numRef>
           </val>
         </ser>
@@ -462,7 +488,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Dashboard'!E14</f>
+              <f>'Dashboard'!E24</f>
             </strRef>
           </tx>
           <spPr>
@@ -480,12 +506,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Dashboard'!$A$15:$A$114</f>
+              <f>'Dashboard'!$A$25:$A$124</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$E$15:$E$114</f>
+              <f>'Dashboard'!$E$25:$E$124</f>
             </numRef>
           </val>
         </ser>
@@ -523,7 +549,7 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <axPos val="r"/>
         <majorGridlines/>
         <title>
           <tx>
@@ -559,12 +585,12 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>7</col>
+      <col>6</col>
       <colOff>0</colOff>
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7920000" cy="5040000"/>
+    <ext cx="7200000" cy="5040000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -604,7 +630,7 @@
     <tableColumn id="16" name="AM024"/>
     <tableColumn id="17" name="AM026"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -630,19 +656,7 @@
     <tableColumn id="16" name="AM024"/>
     <tableColumn id="17" name="AM026"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Parameters" displayName="Parameters" ref="C9:E11" headerRowCount="1">
-  <autoFilter ref="C9:E11"/>
-  <tableColumns count="3">
-    <tableColumn id="3" name="Parameter"/>
-    <tableColumn id="4" name="Value"/>
-    <tableColumn id="5" name="Notes"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight11" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -935,7 +949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q32"/>
+  <dimension ref="A1:Q31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2528,24 +2542,16 @@
         <v>20.41504</v>
       </c>
     </row>
-    <row r="31" ht="32" customHeight="1">
+    <row r="31" ht="30" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>INSTRUCTIONS: Delete the sample rows above (keep Row 1 headers), then paste your data starting at Row 2. Keep Date in Column A; flow/pressure names as column headers. Values of -999 are treated as no-data.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="32" customHeight="1">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>POWER QUERY TIP: This sheet is already set up as an Excel Table ("FlowData"). To connect Power Query: Data → Get Data → From Table/Range → select this table. See the Instructions sheet for the full walkthrough.</t>
+          <t>INSTRUCTIONS: Delete the sample rows above (keep Row 1 headers), then paste your data from Row 2. Date in Column A; flow/pressure names as column headers. -999 = no-data.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="1">
     <mergeCell ref="A31:Q31"/>
-    <mergeCell ref="A32:Q32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -2560,7 +2566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q32"/>
+  <dimension ref="A1:Q31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4153,24 +4159,16 @@
         <v>20.102589</v>
       </c>
     </row>
-    <row r="31" ht="32" customHeight="1">
+    <row r="31" ht="30" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>INSTRUCTIONS: Delete the sample rows above (keep Row 1 headers), then paste your data starting at Row 2. Keep Date in Column A; flow/pressure names as column headers. Values of -999 are treated as no-data.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="32" customHeight="1">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>POWER QUERY TIP: This sheet is already set up as an Excel Table ("PressureData"). To connect Power Query: Data → Get Data → From Table/Range → select this table. See the Instructions sheet for the full walkthrough.</t>
+          <t>INSTRUCTIONS: Delete the sample rows above (keep Row 1 headers), then paste your data from Row 2. Date in Column A; flow/pressure names as column headers. -999 = no-data.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="1">
     <mergeCell ref="A31:Q31"/>
-    <mergeCell ref="A32:Q32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -4185,41 +4183,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F115"/>
+  <dimension ref="A1:F125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="2" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="2" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Flow &amp; Pressure Analysis Dashboard</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
-        <is>
-          <t>CONTROLS</t>
-        </is>
-      </c>
-      <c r="C2" s="9" t="inlineStr">
-        <is>
-          <t>PARAMETERS  (used by Power Query)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="24" customHeight="1">
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Flow Scaling Factor:</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>Pressure Offset:</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Select Flow:</t>
+          <t>Select Flow  ▼</t>
         </is>
       </c>
       <c r="B3" s="11" t="inlineStr">
@@ -4227,2384 +4230,2562 @@
           <t>AL012</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
-        <is>
-          <t>Flow Scaling Factor:</t>
-        </is>
-      </c>
-      <c r="D3" s="12" t="n">
-        <v>1</v>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>Select Pressure  ▼</t>
+        </is>
       </c>
       <c r="E3" s="13" t="inlineStr">
         <is>
-          <t>Multiply flow by this value</t>
-        </is>
-      </c>
-      <c r="F3" s="14" t="inlineStr">
-        <is>
-          <t>← Change me</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>ℹ  -999 = no-data (excluded)</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
-        <is>
-          <t>Pressure Offset:</t>
-        </is>
-      </c>
-      <c r="D4" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="13" t="inlineStr">
-        <is>
-          <t>Add this value to pressure</t>
-        </is>
-      </c>
-      <c r="F4" s="16" t="inlineStr">
-        <is>
-          <t>← Change me</t>
+          <t>AL012</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>All Flows  (current selection highlighted)</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>All Pressures  (current selection highlighted)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="17" t="inlineStr">
-        <is>
-          <t>💡  For large datasets use Power Query + PivotTable — see the Instructions sheet for a full step-by-step guide.</t>
-        </is>
-      </c>
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>AL012</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n"/>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>AL012</t>
+        </is>
+      </c>
+      <c r="E5" s="17" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
-        <is>
-          <t>⚠  After pasting your own data: update the flow dropdown — right-click cell B3 → Data Validation → update the Source range to match your actual column headers.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="6" customHeight="1"/>
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>AL013</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="n"/>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>AL013</t>
+        </is>
+      </c>
+      <c r="E6" s="17" t="n"/>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>AL014</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="n"/>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>AL014</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="n"/>
+    </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>PARAMETER TABLE  (Power Query reads D9:D10)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="C9" s="19" t="inlineStr">
-        <is>
-          <t>Parameter</t>
-        </is>
-      </c>
-      <c r="D9" s="19" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="E9" s="19" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="C10" s="20" t="inlineStr">
-        <is>
-          <t>Flow Scaling Factor</t>
-        </is>
-      </c>
-      <c r="D10" s="21">
-        <f>D3</f>
-        <v/>
-      </c>
-      <c r="E10" s="22" t="inlineStr">
-        <is>
-          <t>Linked to control above (D3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="C11" s="20" t="inlineStr">
-        <is>
-          <t>Pressure Offset</t>
-        </is>
-      </c>
-      <c r="D11" s="21">
-        <f>D4</f>
-        <v/>
-      </c>
-      <c r="E11" s="22" t="inlineStr">
-        <is>
-          <t>Linked to control above (D4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="6" customHeight="1"/>
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>AL023</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="n"/>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>AL023</t>
+        </is>
+      </c>
+      <c r="E8" s="17" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>AL028</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="n"/>
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>AL028</t>
+        </is>
+      </c>
+      <c r="E9" s="17" t="n"/>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>AL029</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="n"/>
+      <c r="D10" s="16" t="inlineStr">
+        <is>
+          <t>AL029</t>
+        </is>
+      </c>
+      <c r="E10" s="17" t="n"/>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>AL035</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="n"/>
+      <c r="D11" s="16" t="inlineStr">
+        <is>
+          <t>AL035</t>
+        </is>
+      </c>
+      <c r="E11" s="17" t="n"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>AL036</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="n"/>
+      <c r="D12" s="16" t="inlineStr">
+        <is>
+          <t>AL036</t>
+        </is>
+      </c>
+      <c r="E12" s="17" t="n"/>
+    </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="23" t="inlineStr">
-        <is>
-          <t>FORMULA TABLE  (live preview — updates when you change B3 / D3 / D4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>AL038</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="n"/>
+      <c r="D13" s="16" t="inlineStr">
+        <is>
+          <t>AL038</t>
+        </is>
+      </c>
+      <c r="E13" s="17" t="n"/>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>AL063</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="n"/>
+      <c r="D14" s="16" t="inlineStr">
+        <is>
+          <t>AL063</t>
+        </is>
+      </c>
+      <c r="E14" s="17" t="n"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>AM005</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="n"/>
+      <c r="D15" s="16" t="inlineStr">
+        <is>
+          <t>AM005</t>
+        </is>
+      </c>
+      <c r="E15" s="17" t="n"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>AM014</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="n"/>
+      <c r="D16" s="16" t="inlineStr">
+        <is>
+          <t>AM014</t>
+        </is>
+      </c>
+      <c r="E16" s="17" t="n"/>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>AM015</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="n"/>
+      <c r="D17" s="16" t="inlineStr">
+        <is>
+          <t>AM015</t>
+        </is>
+      </c>
+      <c r="E17" s="17" t="n"/>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>AM022</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="n"/>
+      <c r="D18" s="16" t="inlineStr">
+        <is>
+          <t>AM022</t>
+        </is>
+      </c>
+      <c r="E18" s="17" t="n"/>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>AM024</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="n"/>
+      <c r="D19" s="16" t="inlineStr">
+        <is>
+          <t>AM024</t>
+        </is>
+      </c>
+      <c r="E19" s="17" t="n"/>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>AM026</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="n"/>
+      <c r="D20" s="16" t="inlineStr">
+        <is>
+          <t>AM026</t>
+        </is>
+      </c>
+      <c r="E20" s="17" t="n"/>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>ℹ  After pasting your own data the lists above update automatically. If the dropdown (B3 / E3) doesn't show your names, right-click the cell → Data Validation → update the Source range to match your column headers. Values of -999 are treated as no-data and excluded from calculations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="18" t="inlineStr">
+        <is>
+          <t>FORMULA TABLE  —  updates automatically when you change the selections or adjustments above</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Flow (Raw)</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C24" s="19" t="inlineStr">
+        <is>
+          <t>Flow Adjusted</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Pressure (Raw)</t>
         </is>
       </c>
-      <c r="D14" s="19" t="inlineStr">
-        <is>
-          <t>Flow Adjusted</t>
-        </is>
-      </c>
-      <c r="E14" s="24" t="inlineStr">
+      <c r="E24" s="20" t="inlineStr">
         <is>
           <t>Pressure Adjusted</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B15" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C15" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D15" s="27">
-        <f>IF(OR(B15="",B15=-999),"",B15*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E15" s="28">
-        <f>IF(OR(C15="",C15=-999),"",C15+$D$4)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" s="29">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B16" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C16" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D16" s="31">
-        <f>IF(OR(B16="",B16=-999),"",B16*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E16" s="32">
-        <f>IF(OR(C16="",C16=-999),"",C16+$D$4)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B17" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C17" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D17" s="27">
-        <f>IF(OR(B17="",B17=-999),"",B17*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E17" s="28">
-        <f>IF(OR(C17="",C17=-999),"",C17+$D$4)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" s="29">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B18" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C18" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D18" s="31">
-        <f>IF(OR(B18="",B18=-999),"",B18*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E18" s="32">
-        <f>IF(OR(C18="",C18=-999),"",C18+$D$4)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B19" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C19" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D19" s="27">
-        <f>IF(OR(B19="",B19=-999),"",B19*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E19" s="28">
-        <f>IF(OR(C19="",C19=-999),"",C19+$D$4)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="29">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B20" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C20" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D20" s="31">
-        <f>IF(OR(B20="",B20=-999),"",B20*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E20" s="32">
-        <f>IF(OR(C20="",C20=-999),"",C20+$D$4)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B21" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C21" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D21" s="27">
-        <f>IF(OR(B21="",B21=-999),"",B21*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E21" s="28">
-        <f>IF(OR(C21="",C21=-999),"",C21+$D$4)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="29">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B22" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C22" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D22" s="31">
-        <f>IF(OR(B22="",B22=-999),"",B22*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E22" s="32">
-        <f>IF(OR(C22="",C22=-999),"",C22+$D$4)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B23" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C23" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D23" s="27">
-        <f>IF(OR(B23="",B23=-999),"",B23*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E23" s="28">
-        <f>IF(OR(C23="",C23=-999),"",C23+$D$4)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="29">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B24" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C24" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D24" s="31">
-        <f>IF(OR(B24="",B24=-999),"",B24*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E24" s="32">
-        <f>IF(OR(C24="",C24=-999),"",C24+$D$4)</f>
-        <v/>
-      </c>
-    </row>
     <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B25" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C25" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D25" s="27">
-        <f>IF(OR(B25="",B25=-999),"",B25*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E25" s="28">
-        <f>IF(OR(C25="",C25=-999),"",C25+$D$4)</f>
+      <c r="A25" s="21">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B25" s="22">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C25" s="23">
+        <f>IF(OR(B25="",B25=-999),"",B25*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D25" s="22">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E25" s="24">
+        <f>IF(OR(D25="",D25=-999),"",D25+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="29">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B26" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C26" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D26" s="31">
-        <f>IF(OR(B26="",B26=-999),"",B26*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E26" s="32">
-        <f>IF(OR(C26="",C26=-999),"",C26+$D$4)</f>
+      <c r="A26" s="25">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B26" s="26">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C26" s="27">
+        <f>IF(OR(B26="",B26=-999),"",B26*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D26" s="26">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E26" s="28">
+        <f>IF(OR(D26="",D26=-999),"",D26+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
-      <c r="A27" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B27" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C27" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D27" s="27">
-        <f>IF(OR(B27="",B27=-999),"",B27*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E27" s="28">
-        <f>IF(OR(C27="",C27=-999),"",C27+$D$4)</f>
+      <c r="A27" s="21">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B27" s="22">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C27" s="23">
+        <f>IF(OR(B27="",B27=-999),"",B27*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D27" s="22">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E27" s="24">
+        <f>IF(OR(D27="",D27=-999),"",D27+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
-      <c r="A28" s="29">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B28" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C28" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D28" s="31">
-        <f>IF(OR(B28="",B28=-999),"",B28*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E28" s="32">
-        <f>IF(OR(C28="",C28=-999),"",C28+$D$4)</f>
+      <c r="A28" s="25">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B28" s="26">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C28" s="27">
+        <f>IF(OR(B28="",B28=-999),"",B28*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D28" s="26">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E28" s="28">
+        <f>IF(OR(D28="",D28=-999),"",D28+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
-      <c r="A29" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B29" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C29" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D29" s="27">
-        <f>IF(OR(B29="",B29=-999),"",B29*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E29" s="28">
-        <f>IF(OR(C29="",C29=-999),"",C29+$D$4)</f>
+      <c r="A29" s="21">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B29" s="22">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C29" s="23">
+        <f>IF(OR(B29="",B29=-999),"",B29*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D29" s="22">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E29" s="24">
+        <f>IF(OR(D29="",D29=-999),"",D29+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="29">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B30" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C30" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D30" s="31">
-        <f>IF(OR(B30="",B30=-999),"",B30*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E30" s="32">
-        <f>IF(OR(C30="",C30=-999),"",C30+$D$4)</f>
+      <c r="A30" s="25">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B30" s="26">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C30" s="27">
+        <f>IF(OR(B30="",B30=-999),"",B30*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D30" s="26">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E30" s="28">
+        <f>IF(OR(D30="",D30=-999),"",D30+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B31" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C31" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D31" s="27">
-        <f>IF(OR(B31="",B31=-999),"",B31*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E31" s="28">
-        <f>IF(OR(C31="",C31=-999),"",C31+$D$4)</f>
+      <c r="A31" s="21">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B31" s="22">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C31" s="23">
+        <f>IF(OR(B31="",B31=-999),"",B31*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D31" s="22">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E31" s="24">
+        <f>IF(OR(D31="",D31=-999),"",D31+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
-      <c r="A32" s="29">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B32" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C32" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D32" s="31">
-        <f>IF(OR(B32="",B32=-999),"",B32*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E32" s="32">
-        <f>IF(OR(C32="",C32=-999),"",C32+$D$4)</f>
+      <c r="A32" s="25">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B32" s="26">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C32" s="27">
+        <f>IF(OR(B32="",B32=-999),"",B32*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D32" s="26">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E32" s="28">
+        <f>IF(OR(D32="",D32=-999),"",D32+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B33" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C33" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D33" s="27">
-        <f>IF(OR(B33="",B33=-999),"",B33*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E33" s="28">
-        <f>IF(OR(C33="",C33=-999),"",C33+$D$4)</f>
+      <c r="A33" s="21">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B33" s="22">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C33" s="23">
+        <f>IF(OR(B33="",B33=-999),"",B33*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D33" s="22">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E33" s="24">
+        <f>IF(OR(D33="",D33=-999),"",D33+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="29">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B34" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C34" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D34" s="31">
-        <f>IF(OR(B34="",B34=-999),"",B34*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E34" s="32">
-        <f>IF(OR(C34="",C34=-999),"",C34+$D$4)</f>
+      <c r="A34" s="25">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B34" s="26">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C34" s="27">
+        <f>IF(OR(B34="",B34=-999),"",B34*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D34" s="26">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E34" s="28">
+        <f>IF(OR(D34="",D34=-999),"",D34+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
-      <c r="A35" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B35" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C35" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D35" s="27">
-        <f>IF(OR(B35="",B35=-999),"",B35*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E35" s="28">
-        <f>IF(OR(C35="",C35=-999),"",C35+$D$4)</f>
+      <c r="A35" s="21">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B35" s="22">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C35" s="23">
+        <f>IF(OR(B35="",B35=-999),"",B35*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D35" s="22">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E35" s="24">
+        <f>IF(OR(D35="",D35=-999),"",D35+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
-      <c r="A36" s="29">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B36" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C36" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D36" s="31">
-        <f>IF(OR(B36="",B36=-999),"",B36*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E36" s="32">
-        <f>IF(OR(C36="",C36=-999),"",C36+$D$4)</f>
+      <c r="A36" s="25">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B36" s="26">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C36" s="27">
+        <f>IF(OR(B36="",B36=-999),"",B36*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D36" s="26">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E36" s="28">
+        <f>IF(OR(D36="",D36=-999),"",D36+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
-      <c r="A37" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B37" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C37" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D37" s="27">
-        <f>IF(OR(B37="",B37=-999),"",B37*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E37" s="28">
-        <f>IF(OR(C37="",C37=-999),"",C37+$D$4)</f>
+      <c r="A37" s="21">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B37" s="22">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C37" s="23">
+        <f>IF(OR(B37="",B37=-999),"",B37*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D37" s="22">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E37" s="24">
+        <f>IF(OR(D37="",D37=-999),"",D37+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
-      <c r="A38" s="29">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B38" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C38" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D38" s="31">
-        <f>IF(OR(B38="",B38=-999),"",B38*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E38" s="32">
-        <f>IF(OR(C38="",C38=-999),"",C38+$D$4)</f>
+      <c r="A38" s="25">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B38" s="26">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C38" s="27">
+        <f>IF(OR(B38="",B38=-999),"",B38*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D38" s="26">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E38" s="28">
+        <f>IF(OR(D38="",D38=-999),"",D38+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
-      <c r="A39" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B39" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C39" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D39" s="27">
-        <f>IF(OR(B39="",B39=-999),"",B39*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E39" s="28">
-        <f>IF(OR(C39="",C39=-999),"",C39+$D$4)</f>
+      <c r="A39" s="21">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B39" s="22">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C39" s="23">
+        <f>IF(OR(B39="",B39=-999),"",B39*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D39" s="22">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E39" s="24">
+        <f>IF(OR(D39="",D39=-999),"",D39+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
-      <c r="A40" s="29">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B40" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C40" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D40" s="31">
-        <f>IF(OR(B40="",B40=-999),"",B40*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E40" s="32">
-        <f>IF(OR(C40="",C40=-999),"",C40+$D$4)</f>
+      <c r="A40" s="25">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B40" s="26">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C40" s="27">
+        <f>IF(OR(B40="",B40=-999),"",B40*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D40" s="26">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E40" s="28">
+        <f>IF(OR(D40="",D40=-999),"",D40+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
-      <c r="A41" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B41" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C41" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D41" s="27">
-        <f>IF(OR(B41="",B41=-999),"",B41*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E41" s="28">
-        <f>IF(OR(C41="",C41=-999),"",C41+$D$4)</f>
+      <c r="A41" s="21">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B41" s="22">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C41" s="23">
+        <f>IF(OR(B41="",B41=-999),"",B41*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D41" s="22">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E41" s="24">
+        <f>IF(OR(D41="",D41=-999),"",D41+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
-      <c r="A42" s="29">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B42" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C42" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D42" s="31">
-        <f>IF(OR(B42="",B42=-999),"",B42*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E42" s="32">
-        <f>IF(OR(C42="",C42=-999),"",C42+$D$4)</f>
+      <c r="A42" s="25">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B42" s="26">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C42" s="27">
+        <f>IF(OR(B42="",B42=-999),"",B42*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D42" s="26">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E42" s="28">
+        <f>IF(OR(D42="",D42=-999),"",D42+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
-      <c r="A43" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B43" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C43" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D43" s="27">
-        <f>IF(OR(B43="",B43=-999),"",B43*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E43" s="28">
-        <f>IF(OR(C43="",C43=-999),"",C43+$D$4)</f>
+      <c r="A43" s="21">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B43" s="22">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C43" s="23">
+        <f>IF(OR(B43="",B43=-999),"",B43*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D43" s="22">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E43" s="24">
+        <f>IF(OR(D43="",D43=-999),"",D43+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
-      <c r="A44" s="29">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B44" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C44" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D44" s="31">
-        <f>IF(OR(B44="",B44=-999),"",B44*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E44" s="32">
-        <f>IF(OR(C44="",C44=-999),"",C44+$D$4)</f>
+      <c r="A44" s="25">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B44" s="26">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C44" s="27">
+        <f>IF(OR(B44="",B44=-999),"",B44*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D44" s="26">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E44" s="28">
+        <f>IF(OR(D44="",D44=-999),"",D44+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
-      <c r="A45" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B45" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C45" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D45" s="27">
-        <f>IF(OR(B45="",B45=-999),"",B45*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E45" s="28">
-        <f>IF(OR(C45="",C45=-999),"",C45+$D$4)</f>
+      <c r="A45" s="21">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B45" s="22">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C45" s="23">
+        <f>IF(OR(B45="",B45=-999),"",B45*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D45" s="22">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E45" s="24">
+        <f>IF(OR(D45="",D45=-999),"",D45+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
-      <c r="A46" s="29">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B46" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C46" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D46" s="31">
-        <f>IF(OR(B46="",B46=-999),"",B46*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E46" s="32">
-        <f>IF(OR(C46="",C46=-999),"",C46+$D$4)</f>
+      <c r="A46" s="25">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B46" s="26">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C46" s="27">
+        <f>IF(OR(B46="",B46=-999),"",B46*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D46" s="26">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E46" s="28">
+        <f>IF(OR(D46="",D46=-999),"",D46+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
-      <c r="A47" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B47" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C47" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D47" s="27">
-        <f>IF(OR(B47="",B47=-999),"",B47*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E47" s="28">
-        <f>IF(OR(C47="",C47=-999),"",C47+$D$4)</f>
+      <c r="A47" s="21">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B47" s="22">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C47" s="23">
+        <f>IF(OR(B47="",B47=-999),"",B47*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D47" s="22">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E47" s="24">
+        <f>IF(OR(D47="",D47=-999),"",D47+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
-      <c r="A48" s="29">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B48" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C48" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D48" s="31">
-        <f>IF(OR(B48="",B48=-999),"",B48*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E48" s="32">
-        <f>IF(OR(C48="",C48=-999),"",C48+$D$4)</f>
+      <c r="A48" s="25">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B48" s="26">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C48" s="27">
+        <f>IF(OR(B48="",B48=-999),"",B48*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D48" s="26">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E48" s="28">
+        <f>IF(OR(D48="",D48=-999),"",D48+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1">
-      <c r="A49" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B49" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C49" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D49" s="27">
-        <f>IF(OR(B49="",B49=-999),"",B49*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E49" s="28">
-        <f>IF(OR(C49="",C49=-999),"",C49+$D$4)</f>
+      <c r="A49" s="21">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B49" s="22">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C49" s="23">
+        <f>IF(OR(B49="",B49=-999),"",B49*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D49" s="22">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E49" s="24">
+        <f>IF(OR(D49="",D49=-999),"",D49+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1">
-      <c r="A50" s="29">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B50" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C50" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D50" s="31">
-        <f>IF(OR(B50="",B50=-999),"",B50*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E50" s="32">
-        <f>IF(OR(C50="",C50=-999),"",C50+$D$4)</f>
+      <c r="A50" s="25">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B50" s="26">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C50" s="27">
+        <f>IF(OR(B50="",B50=-999),"",B50*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D50" s="26">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E50" s="28">
+        <f>IF(OR(D50="",D50=-999),"",D50+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1">
-      <c r="A51" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B51" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C51" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D51" s="27">
-        <f>IF(OR(B51="",B51=-999),"",B51*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E51" s="28">
-        <f>IF(OR(C51="",C51=-999),"",C51+$D$4)</f>
+      <c r="A51" s="21">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B51" s="22">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C51" s="23">
+        <f>IF(OR(B51="",B51=-999),"",B51*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D51" s="22">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E51" s="24">
+        <f>IF(OR(D51="",D51=-999),"",D51+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1">
-      <c r="A52" s="29">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B52" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C52" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D52" s="31">
-        <f>IF(OR(B52="",B52=-999),"",B52*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E52" s="32">
-        <f>IF(OR(C52="",C52=-999),"",C52+$D$4)</f>
+      <c r="A52" s="25">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B52" s="26">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C52" s="27">
+        <f>IF(OR(B52="",B52=-999),"",B52*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D52" s="26">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E52" s="28">
+        <f>IF(OR(D52="",D52=-999),"",D52+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1">
-      <c r="A53" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B53" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C53" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D53" s="27">
-        <f>IF(OR(B53="",B53=-999),"",B53*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E53" s="28">
-        <f>IF(OR(C53="",C53=-999),"",C53+$D$4)</f>
+      <c r="A53" s="21">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B53" s="22">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C53" s="23">
+        <f>IF(OR(B53="",B53=-999),"",B53*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D53" s="22">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E53" s="24">
+        <f>IF(OR(D53="",D53=-999),"",D53+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1">
-      <c r="A54" s="29">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B54" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C54" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D54" s="31">
-        <f>IF(OR(B54="",B54=-999),"",B54*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E54" s="32">
-        <f>IF(OR(C54="",C54=-999),"",C54+$D$4)</f>
+      <c r="A54" s="25">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B54" s="26">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C54" s="27">
+        <f>IF(OR(B54="",B54=-999),"",B54*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D54" s="26">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E54" s="28">
+        <f>IF(OR(D54="",D54=-999),"",D54+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1">
-      <c r="A55" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B55" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C55" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D55" s="27">
-        <f>IF(OR(B55="",B55=-999),"",B55*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E55" s="28">
-        <f>IF(OR(C55="",C55=-999),"",C55+$D$4)</f>
+      <c r="A55" s="21">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B55" s="22">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C55" s="23">
+        <f>IF(OR(B55="",B55=-999),"",B55*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D55" s="22">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E55" s="24">
+        <f>IF(OR(D55="",D55=-999),"",D55+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1">
-      <c r="A56" s="29">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B56" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C56" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D56" s="31">
-        <f>IF(OR(B56="",B56=-999),"",B56*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E56" s="32">
-        <f>IF(OR(C56="",C56=-999),"",C56+$D$4)</f>
+      <c r="A56" s="25">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B56" s="26">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C56" s="27">
+        <f>IF(OR(B56="",B56=-999),"",B56*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D56" s="26">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E56" s="28">
+        <f>IF(OR(D56="",D56=-999),"",D56+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1">
-      <c r="A57" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B57" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C57" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D57" s="27">
-        <f>IF(OR(B57="",B57=-999),"",B57*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E57" s="28">
-        <f>IF(OR(C57="",C57=-999),"",C57+$D$4)</f>
+      <c r="A57" s="21">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B57" s="22">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C57" s="23">
+        <f>IF(OR(B57="",B57=-999),"",B57*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D57" s="22">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E57" s="24">
+        <f>IF(OR(D57="",D57=-999),"",D57+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1">
-      <c r="A58" s="29">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B58" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C58" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D58" s="31">
-        <f>IF(OR(B58="",B58=-999),"",B58*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E58" s="32">
-        <f>IF(OR(C58="",C58=-999),"",C58+$D$4)</f>
+      <c r="A58" s="25">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B58" s="26">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C58" s="27">
+        <f>IF(OR(B58="",B58=-999),"",B58*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D58" s="26">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E58" s="28">
+        <f>IF(OR(D58="",D58=-999),"",D58+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1">
-      <c r="A59" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B59" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C59" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D59" s="27">
-        <f>IF(OR(B59="",B59=-999),"",B59*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E59" s="28">
-        <f>IF(OR(C59="",C59=-999),"",C59+$D$4)</f>
+      <c r="A59" s="21">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B59" s="22">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C59" s="23">
+        <f>IF(OR(B59="",B59=-999),"",B59*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D59" s="22">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E59" s="24">
+        <f>IF(OR(D59="",D59=-999),"",D59+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1">
-      <c r="A60" s="29">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B60" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C60" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D60" s="31">
-        <f>IF(OR(B60="",B60=-999),"",B60*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E60" s="32">
-        <f>IF(OR(C60="",C60=-999),"",C60+$D$4)</f>
+      <c r="A60" s="25">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B60" s="26">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C60" s="27">
+        <f>IF(OR(B60="",B60=-999),"",B60*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D60" s="26">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E60" s="28">
+        <f>IF(OR(D60="",D60=-999),"",D60+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1">
-      <c r="A61" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B61" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C61" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D61" s="27">
-        <f>IF(OR(B61="",B61=-999),"",B61*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E61" s="28">
-        <f>IF(OR(C61="",C61=-999),"",C61+$D$4)</f>
+      <c r="A61" s="21">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B61" s="22">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C61" s="23">
+        <f>IF(OR(B61="",B61=-999),"",B61*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D61" s="22">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E61" s="24">
+        <f>IF(OR(D61="",D61=-999),"",D61+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1">
-      <c r="A62" s="29">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B62" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C62" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D62" s="31">
-        <f>IF(OR(B62="",B62=-999),"",B62*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E62" s="32">
-        <f>IF(OR(C62="",C62=-999),"",C62+$D$4)</f>
+      <c r="A62" s="25">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B62" s="26">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C62" s="27">
+        <f>IF(OR(B62="",B62=-999),"",B62*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D62" s="26">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E62" s="28">
+        <f>IF(OR(D62="",D62=-999),"",D62+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1">
-      <c r="A63" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B63" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C63" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D63" s="27">
-        <f>IF(OR(B63="",B63=-999),"",B63*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E63" s="28">
-        <f>IF(OR(C63="",C63=-999),"",C63+$D$4)</f>
+      <c r="A63" s="21">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B63" s="22">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C63" s="23">
+        <f>IF(OR(B63="",B63=-999),"",B63*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D63" s="22">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E63" s="24">
+        <f>IF(OR(D63="",D63=-999),"",D63+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1">
-      <c r="A64" s="29">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B64" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C64" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D64" s="31">
-        <f>IF(OR(B64="",B64=-999),"",B64*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E64" s="32">
-        <f>IF(OR(C64="",C64=-999),"",C64+$D$4)</f>
+      <c r="A64" s="25">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B64" s="26">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C64" s="27">
+        <f>IF(OR(B64="",B64=-999),"",B64*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D64" s="26">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E64" s="28">
+        <f>IF(OR(D64="",D64=-999),"",D64+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1">
-      <c r="A65" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B65" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C65" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D65" s="27">
-        <f>IF(OR(B65="",B65=-999),"",B65*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E65" s="28">
-        <f>IF(OR(C65="",C65=-999),"",C65+$D$4)</f>
+      <c r="A65" s="21">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B65" s="22">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C65" s="23">
+        <f>IF(OR(B65="",B65=-999),"",B65*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D65" s="22">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E65" s="24">
+        <f>IF(OR(D65="",D65=-999),"",D65+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1">
-      <c r="A66" s="29">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B66" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C66" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D66" s="31">
-        <f>IF(OR(B66="",B66=-999),"",B66*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E66" s="32">
-        <f>IF(OR(C66="",C66=-999),"",C66+$D$4)</f>
+      <c r="A66" s="25">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B66" s="26">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C66" s="27">
+        <f>IF(OR(B66="",B66=-999),"",B66*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D66" s="26">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E66" s="28">
+        <f>IF(OR(D66="",D66=-999),"",D66+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1">
-      <c r="A67" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B67" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C67" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D67" s="27">
-        <f>IF(OR(B67="",B67=-999),"",B67*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E67" s="28">
-        <f>IF(OR(C67="",C67=-999),"",C67+$D$4)</f>
+      <c r="A67" s="21">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B67" s="22">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C67" s="23">
+        <f>IF(OR(B67="",B67=-999),"",B67*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D67" s="22">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E67" s="24">
+        <f>IF(OR(D67="",D67=-999),"",D67+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1">
-      <c r="A68" s="29">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B68" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C68" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D68" s="31">
-        <f>IF(OR(B68="",B68=-999),"",B68*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E68" s="32">
-        <f>IF(OR(C68="",C68=-999),"",C68+$D$4)</f>
+      <c r="A68" s="25">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B68" s="26">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C68" s="27">
+        <f>IF(OR(B68="",B68=-999),"",B68*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D68" s="26">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E68" s="28">
+        <f>IF(OR(D68="",D68=-999),"",D68+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1">
-      <c r="A69" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B69" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C69" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D69" s="27">
-        <f>IF(OR(B69="",B69=-999),"",B69*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E69" s="28">
-        <f>IF(OR(C69="",C69=-999),"",C69+$D$4)</f>
+      <c r="A69" s="21">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B69" s="22">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C69" s="23">
+        <f>IF(OR(B69="",B69=-999),"",B69*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D69" s="22">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E69" s="24">
+        <f>IF(OR(D69="",D69=-999),"",D69+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1">
-      <c r="A70" s="29">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B70" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C70" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D70" s="31">
-        <f>IF(OR(B70="",B70=-999),"",B70*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E70" s="32">
-        <f>IF(OR(C70="",C70=-999),"",C70+$D$4)</f>
+      <c r="A70" s="25">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B70" s="26">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C70" s="27">
+        <f>IF(OR(B70="",B70=-999),"",B70*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D70" s="26">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E70" s="28">
+        <f>IF(OR(D70="",D70=-999),"",D70+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1">
-      <c r="A71" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B71" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C71" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D71" s="27">
-        <f>IF(OR(B71="",B71=-999),"",B71*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E71" s="28">
-        <f>IF(OR(C71="",C71=-999),"",C71+$D$4)</f>
+      <c r="A71" s="21">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B71" s="22">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C71" s="23">
+        <f>IF(OR(B71="",B71=-999),"",B71*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D71" s="22">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E71" s="24">
+        <f>IF(OR(D71="",D71=-999),"",D71+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1">
-      <c r="A72" s="29">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B72" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C72" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D72" s="31">
-        <f>IF(OR(B72="",B72=-999),"",B72*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E72" s="32">
-        <f>IF(OR(C72="",C72=-999),"",C72+$D$4)</f>
+      <c r="A72" s="25">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B72" s="26">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C72" s="27">
+        <f>IF(OR(B72="",B72=-999),"",B72*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D72" s="26">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E72" s="28">
+        <f>IF(OR(D72="",D72=-999),"",D72+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1">
-      <c r="A73" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B73" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C73" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D73" s="27">
-        <f>IF(OR(B73="",B73=-999),"",B73*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E73" s="28">
-        <f>IF(OR(C73="",C73=-999),"",C73+$D$4)</f>
+      <c r="A73" s="21">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B73" s="22">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C73" s="23">
+        <f>IF(OR(B73="",B73=-999),"",B73*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D73" s="22">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E73" s="24">
+        <f>IF(OR(D73="",D73=-999),"",D73+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1">
-      <c r="A74" s="29">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B74" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C74" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D74" s="31">
-        <f>IF(OR(B74="",B74=-999),"",B74*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E74" s="32">
-        <f>IF(OR(C74="",C74=-999),"",C74+$D$4)</f>
+      <c r="A74" s="25">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B74" s="26">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C74" s="27">
+        <f>IF(OR(B74="",B74=-999),"",B74*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D74" s="26">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E74" s="28">
+        <f>IF(OR(D74="",D74=-999),"",D74+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1">
-      <c r="A75" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B75" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C75" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D75" s="27">
-        <f>IF(OR(B75="",B75=-999),"",B75*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E75" s="28">
-        <f>IF(OR(C75="",C75=-999),"",C75+$D$4)</f>
+      <c r="A75" s="21">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B75" s="22">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C75" s="23">
+        <f>IF(OR(B75="",B75=-999),"",B75*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D75" s="22">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E75" s="24">
+        <f>IF(OR(D75="",D75=-999),"",D75+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="76" ht="15" customHeight="1">
-      <c r="A76" s="29">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B76" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C76" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D76" s="31">
-        <f>IF(OR(B76="",B76=-999),"",B76*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E76" s="32">
-        <f>IF(OR(C76="",C76=-999),"",C76+$D$4)</f>
+      <c r="A76" s="25">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B76" s="26">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C76" s="27">
+        <f>IF(OR(B76="",B76=-999),"",B76*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D76" s="26">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E76" s="28">
+        <f>IF(OR(D76="",D76=-999),"",D76+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1">
-      <c r="A77" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B77" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C77" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D77" s="27">
-        <f>IF(OR(B77="",B77=-999),"",B77*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E77" s="28">
-        <f>IF(OR(C77="",C77=-999),"",C77+$D$4)</f>
+      <c r="A77" s="21">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B77" s="22">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C77" s="23">
+        <f>IF(OR(B77="",B77=-999),"",B77*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D77" s="22">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E77" s="24">
+        <f>IF(OR(D77="",D77=-999),"",D77+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1">
-      <c r="A78" s="29">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B78" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C78" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D78" s="31">
-        <f>IF(OR(B78="",B78=-999),"",B78*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E78" s="32">
-        <f>IF(OR(C78="",C78=-999),"",C78+$D$4)</f>
+      <c r="A78" s="25">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B78" s="26">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C78" s="27">
+        <f>IF(OR(B78="",B78=-999),"",B78*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D78" s="26">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E78" s="28">
+        <f>IF(OR(D78="",D78=-999),"",D78+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1">
-      <c r="A79" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B79" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C79" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D79" s="27">
-        <f>IF(OR(B79="",B79=-999),"",B79*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E79" s="28">
-        <f>IF(OR(C79="",C79=-999),"",C79+$D$4)</f>
+      <c r="A79" s="21">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B79" s="22">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C79" s="23">
+        <f>IF(OR(B79="",B79=-999),"",B79*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D79" s="22">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E79" s="24">
+        <f>IF(OR(D79="",D79=-999),"",D79+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1">
-      <c r="A80" s="29">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B80" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C80" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D80" s="31">
-        <f>IF(OR(B80="",B80=-999),"",B80*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E80" s="32">
-        <f>IF(OR(C80="",C80=-999),"",C80+$D$4)</f>
+      <c r="A80" s="25">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B80" s="26">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C80" s="27">
+        <f>IF(OR(B80="",B80=-999),"",B80*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D80" s="26">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E80" s="28">
+        <f>IF(OR(D80="",D80=-999),"",D80+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1">
-      <c r="A81" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B81" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C81" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D81" s="27">
-        <f>IF(OR(B81="",B81=-999),"",B81*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E81" s="28">
-        <f>IF(OR(C81="",C81=-999),"",C81+$D$4)</f>
+      <c r="A81" s="21">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B81" s="22">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C81" s="23">
+        <f>IF(OR(B81="",B81=-999),"",B81*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D81" s="22">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E81" s="24">
+        <f>IF(OR(D81="",D81=-999),"",D81+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1">
-      <c r="A82" s="29">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B82" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C82" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D82" s="31">
-        <f>IF(OR(B82="",B82=-999),"",B82*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E82" s="32">
-        <f>IF(OR(C82="",C82=-999),"",C82+$D$4)</f>
+      <c r="A82" s="25">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B82" s="26">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C82" s="27">
+        <f>IF(OR(B82="",B82=-999),"",B82*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D82" s="26">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E82" s="28">
+        <f>IF(OR(D82="",D82=-999),"",D82+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1">
-      <c r="A83" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B83" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C83" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D83" s="27">
-        <f>IF(OR(B83="",B83=-999),"",B83*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E83" s="28">
-        <f>IF(OR(C83="",C83=-999),"",C83+$D$4)</f>
+      <c r="A83" s="21">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B83" s="22">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C83" s="23">
+        <f>IF(OR(B83="",B83=-999),"",B83*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D83" s="22">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E83" s="24">
+        <f>IF(OR(D83="",D83=-999),"",D83+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1">
-      <c r="A84" s="29">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B84" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C84" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D84" s="31">
-        <f>IF(OR(B84="",B84=-999),"",B84*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E84" s="32">
-        <f>IF(OR(C84="",C84=-999),"",C84+$D$4)</f>
+      <c r="A84" s="25">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B84" s="26">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C84" s="27">
+        <f>IF(OR(B84="",B84=-999),"",B84*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D84" s="26">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E84" s="28">
+        <f>IF(OR(D84="",D84=-999),"",D84+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1">
-      <c r="A85" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B85" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C85" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D85" s="27">
-        <f>IF(OR(B85="",B85=-999),"",B85*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E85" s="28">
-        <f>IF(OR(C85="",C85=-999),"",C85+$D$4)</f>
+      <c r="A85" s="21">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B85" s="22">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C85" s="23">
+        <f>IF(OR(B85="",B85=-999),"",B85*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D85" s="22">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E85" s="24">
+        <f>IF(OR(D85="",D85=-999),"",D85+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1">
-      <c r="A86" s="29">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B86" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C86" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D86" s="31">
-        <f>IF(OR(B86="",B86=-999),"",B86*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E86" s="32">
-        <f>IF(OR(C86="",C86=-999),"",C86+$D$4)</f>
+      <c r="A86" s="25">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B86" s="26">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C86" s="27">
+        <f>IF(OR(B86="",B86=-999),"",B86*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D86" s="26">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E86" s="28">
+        <f>IF(OR(D86="",D86=-999),"",D86+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1">
-      <c r="A87" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B87" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C87" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D87" s="27">
-        <f>IF(OR(B87="",B87=-999),"",B87*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E87" s="28">
-        <f>IF(OR(C87="",C87=-999),"",C87+$D$4)</f>
+      <c r="A87" s="21">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B87" s="22">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C87" s="23">
+        <f>IF(OR(B87="",B87=-999),"",B87*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D87" s="22">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E87" s="24">
+        <f>IF(OR(D87="",D87=-999),"",D87+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1">
-      <c r="A88" s="29">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B88" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C88" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D88" s="31">
-        <f>IF(OR(B88="",B88=-999),"",B88*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E88" s="32">
-        <f>IF(OR(C88="",C88=-999),"",C88+$D$4)</f>
+      <c r="A88" s="25">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B88" s="26">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C88" s="27">
+        <f>IF(OR(B88="",B88=-999),"",B88*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D88" s="26">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E88" s="28">
+        <f>IF(OR(D88="",D88=-999),"",D88+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="89" ht="15" customHeight="1">
-      <c r="A89" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B89" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C89" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D89" s="27">
-        <f>IF(OR(B89="",B89=-999),"",B89*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E89" s="28">
-        <f>IF(OR(C89="",C89=-999),"",C89+$D$4)</f>
+      <c r="A89" s="21">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B89" s="22">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C89" s="23">
+        <f>IF(OR(B89="",B89=-999),"",B89*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D89" s="22">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E89" s="24">
+        <f>IF(OR(D89="",D89=-999),"",D89+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1">
-      <c r="A90" s="29">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B90" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C90" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D90" s="31">
-        <f>IF(OR(B90="",B90=-999),"",B90*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E90" s="32">
-        <f>IF(OR(C90="",C90=-999),"",C90+$D$4)</f>
+      <c r="A90" s="25">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B90" s="26">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C90" s="27">
+        <f>IF(OR(B90="",B90=-999),"",B90*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D90" s="26">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E90" s="28">
+        <f>IF(OR(D90="",D90=-999),"",D90+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="91" ht="15" customHeight="1">
-      <c r="A91" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B91" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C91" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D91" s="27">
-        <f>IF(OR(B91="",B91=-999),"",B91*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E91" s="28">
-        <f>IF(OR(C91="",C91=-999),"",C91+$D$4)</f>
+      <c r="A91" s="21">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B91" s="22">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C91" s="23">
+        <f>IF(OR(B91="",B91=-999),"",B91*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D91" s="22">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E91" s="24">
+        <f>IF(OR(D91="",D91=-999),"",D91+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="92" ht="15" customHeight="1">
-      <c r="A92" s="29">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B92" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C92" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D92" s="31">
-        <f>IF(OR(B92="",B92=-999),"",B92*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E92" s="32">
-        <f>IF(OR(C92="",C92=-999),"",C92+$D$4)</f>
+      <c r="A92" s="25">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B92" s="26">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C92" s="27">
+        <f>IF(OR(B92="",B92=-999),"",B92*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D92" s="26">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E92" s="28">
+        <f>IF(OR(D92="",D92=-999),"",D92+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="93" ht="15" customHeight="1">
-      <c r="A93" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B93" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C93" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D93" s="27">
-        <f>IF(OR(B93="",B93=-999),"",B93*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E93" s="28">
-        <f>IF(OR(C93="",C93=-999),"",C93+$D$4)</f>
+      <c r="A93" s="21">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B93" s="22">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C93" s="23">
+        <f>IF(OR(B93="",B93=-999),"",B93*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D93" s="22">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E93" s="24">
+        <f>IF(OR(D93="",D93=-999),"",D93+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="94" ht="15" customHeight="1">
-      <c r="A94" s="29">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B94" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C94" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D94" s="31">
-        <f>IF(OR(B94="",B94=-999),"",B94*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E94" s="32">
-        <f>IF(OR(C94="",C94=-999),"",C94+$D$4)</f>
+      <c r="A94" s="25">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B94" s="26">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C94" s="27">
+        <f>IF(OR(B94="",B94=-999),"",B94*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D94" s="26">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E94" s="28">
+        <f>IF(OR(D94="",D94=-999),"",D94+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1">
-      <c r="A95" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B95" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C95" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D95" s="27">
-        <f>IF(OR(B95="",B95=-999),"",B95*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E95" s="28">
-        <f>IF(OR(C95="",C95=-999),"",C95+$D$4)</f>
+      <c r="A95" s="21">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B95" s="22">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C95" s="23">
+        <f>IF(OR(B95="",B95=-999),"",B95*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D95" s="22">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E95" s="24">
+        <f>IF(OR(D95="",D95=-999),"",D95+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="96" ht="15" customHeight="1">
-      <c r="A96" s="29">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B96" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C96" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D96" s="31">
-        <f>IF(OR(B96="",B96=-999),"",B96*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E96" s="32">
-        <f>IF(OR(C96="",C96=-999),"",C96+$D$4)</f>
+      <c r="A96" s="25">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B96" s="26">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C96" s="27">
+        <f>IF(OR(B96="",B96=-999),"",B96*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D96" s="26">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E96" s="28">
+        <f>IF(OR(D96="",D96=-999),"",D96+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="97" ht="15" customHeight="1">
-      <c r="A97" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B97" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C97" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D97" s="27">
-        <f>IF(OR(B97="",B97=-999),"",B97*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E97" s="28">
-        <f>IF(OR(C97="",C97=-999),"",C97+$D$4)</f>
+      <c r="A97" s="21">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B97" s="22">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C97" s="23">
+        <f>IF(OR(B97="",B97=-999),"",B97*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D97" s="22">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E97" s="24">
+        <f>IF(OR(D97="",D97=-999),"",D97+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="98" ht="15" customHeight="1">
-      <c r="A98" s="29">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B98" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C98" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D98" s="31">
-        <f>IF(OR(B98="",B98=-999),"",B98*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E98" s="32">
-        <f>IF(OR(C98="",C98=-999),"",C98+$D$4)</f>
+      <c r="A98" s="25">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B98" s="26">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C98" s="27">
+        <f>IF(OR(B98="",B98=-999),"",B98*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D98" s="26">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E98" s="28">
+        <f>IF(OR(D98="",D98=-999),"",D98+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="99" ht="15" customHeight="1">
-      <c r="A99" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B99" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C99" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D99" s="27">
-        <f>IF(OR(B99="",B99=-999),"",B99*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E99" s="28">
-        <f>IF(OR(C99="",C99=-999),"",C99+$D$4)</f>
+      <c r="A99" s="21">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B99" s="22">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C99" s="23">
+        <f>IF(OR(B99="",B99=-999),"",B99*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D99" s="22">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E99" s="24">
+        <f>IF(OR(D99="",D99=-999),"",D99+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1">
-      <c r="A100" s="29">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B100" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C100" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D100" s="31">
-        <f>IF(OR(B100="",B100=-999),"",B100*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E100" s="32">
-        <f>IF(OR(C100="",C100=-999),"",C100+$D$4)</f>
+      <c r="A100" s="25">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B100" s="26">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C100" s="27">
+        <f>IF(OR(B100="",B100=-999),"",B100*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D100" s="26">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E100" s="28">
+        <f>IF(OR(D100="",D100=-999),"",D100+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="101" ht="15" customHeight="1">
-      <c r="A101" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B101" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C101" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D101" s="27">
-        <f>IF(OR(B101="",B101=-999),"",B101*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E101" s="28">
-        <f>IF(OR(C101="",C101=-999),"",C101+$D$4)</f>
+      <c r="A101" s="21">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B101" s="22">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C101" s="23">
+        <f>IF(OR(B101="",B101=-999),"",B101*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D101" s="22">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E101" s="24">
+        <f>IF(OR(D101="",D101=-999),"",D101+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="102" ht="15" customHeight="1">
-      <c r="A102" s="29">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B102" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C102" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D102" s="31">
-        <f>IF(OR(B102="",B102=-999),"",B102*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E102" s="32">
-        <f>IF(OR(C102="",C102=-999),"",C102+$D$4)</f>
+      <c r="A102" s="25">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B102" s="26">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C102" s="27">
+        <f>IF(OR(B102="",B102=-999),"",B102*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D102" s="26">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E102" s="28">
+        <f>IF(OR(D102="",D102=-999),"",D102+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="103" ht="15" customHeight="1">
-      <c r="A103" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B103" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C103" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D103" s="27">
-        <f>IF(OR(B103="",B103=-999),"",B103*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E103" s="28">
-        <f>IF(OR(C103="",C103=-999),"",C103+$D$4)</f>
+      <c r="A103" s="21">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B103" s="22">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C103" s="23">
+        <f>IF(OR(B103="",B103=-999),"",B103*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D103" s="22">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E103" s="24">
+        <f>IF(OR(D103="",D103=-999),"",D103+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="104" ht="15" customHeight="1">
-      <c r="A104" s="29">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B104" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C104" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D104" s="31">
-        <f>IF(OR(B104="",B104=-999),"",B104*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E104" s="32">
-        <f>IF(OR(C104="",C104=-999),"",C104+$D$4)</f>
+      <c r="A104" s="25">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B104" s="26">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C104" s="27">
+        <f>IF(OR(B104="",B104=-999),"",B104*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D104" s="26">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E104" s="28">
+        <f>IF(OR(D104="",D104=-999),"",D104+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="105" ht="15" customHeight="1">
-      <c r="A105" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B105" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C105" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D105" s="27">
-        <f>IF(OR(B105="",B105=-999),"",B105*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E105" s="28">
-        <f>IF(OR(C105="",C105=-999),"",C105+$D$4)</f>
+      <c r="A105" s="21">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B105" s="22">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C105" s="23">
+        <f>IF(OR(B105="",B105=-999),"",B105*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D105" s="22">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E105" s="24">
+        <f>IF(OR(D105="",D105=-999),"",D105+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="106" ht="15" customHeight="1">
-      <c r="A106" s="29">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B106" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C106" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D106" s="31">
-        <f>IF(OR(B106="",B106=-999),"",B106*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E106" s="32">
-        <f>IF(OR(C106="",C106=-999),"",C106+$D$4)</f>
+      <c r="A106" s="25">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B106" s="26">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C106" s="27">
+        <f>IF(OR(B106="",B106=-999),"",B106*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D106" s="26">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E106" s="28">
+        <f>IF(OR(D106="",D106=-999),"",D106+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1">
-      <c r="A107" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B107" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C107" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D107" s="27">
-        <f>IF(OR(B107="",B107=-999),"",B107*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E107" s="28">
-        <f>IF(OR(C107="",C107=-999),"",C107+$D$4)</f>
+      <c r="A107" s="21">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B107" s="22">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C107" s="23">
+        <f>IF(OR(B107="",B107=-999),"",B107*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D107" s="22">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E107" s="24">
+        <f>IF(OR(D107="",D107=-999),"",D107+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="108" ht="15" customHeight="1">
-      <c r="A108" s="29">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B108" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C108" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D108" s="31">
-        <f>IF(OR(B108="",B108=-999),"",B108*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E108" s="32">
-        <f>IF(OR(C108="",C108=-999),"",C108+$D$4)</f>
+      <c r="A108" s="25">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B108" s="26">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C108" s="27">
+        <f>IF(OR(B108="",B108=-999),"",B108*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D108" s="26">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E108" s="28">
+        <f>IF(OR(D108="",D108=-999),"",D108+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="109" ht="15" customHeight="1">
-      <c r="A109" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B109" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C109" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D109" s="27">
-        <f>IF(OR(B109="",B109=-999),"",B109*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E109" s="28">
-        <f>IF(OR(C109="",C109=-999),"",C109+$D$4)</f>
+      <c r="A109" s="21">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B109" s="22">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C109" s="23">
+        <f>IF(OR(B109="",B109=-999),"",B109*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D109" s="22">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E109" s="24">
+        <f>IF(OR(D109="",D109=-999),"",D109+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="110" ht="15" customHeight="1">
-      <c r="A110" s="29">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B110" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C110" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D110" s="31">
-        <f>IF(OR(B110="",B110=-999),"",B110*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E110" s="32">
-        <f>IF(OR(C110="",C110=-999),"",C110+$D$4)</f>
+      <c r="A110" s="25">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B110" s="26">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C110" s="27">
+        <f>IF(OR(B110="",B110=-999),"",B110*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D110" s="26">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E110" s="28">
+        <f>IF(OR(D110="",D110=-999),"",D110+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="111" ht="15" customHeight="1">
-      <c r="A111" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B111" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C111" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D111" s="27">
-        <f>IF(OR(B111="",B111=-999),"",B111*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E111" s="28">
-        <f>IF(OR(C111="",C111=-999),"",C111+$D$4)</f>
+      <c r="A111" s="21">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B111" s="22">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C111" s="23">
+        <f>IF(OR(B111="",B111=-999),"",B111*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D111" s="22">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E111" s="24">
+        <f>IF(OR(D111="",D111=-999),"",D111+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="112" ht="15" customHeight="1">
-      <c r="A112" s="29">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B112" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C112" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D112" s="31">
-        <f>IF(OR(B112="",B112=-999),"",B112*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E112" s="32">
-        <f>IF(OR(C112="",C112=-999),"",C112+$D$4)</f>
+      <c r="A112" s="25">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B112" s="26">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C112" s="27">
+        <f>IF(OR(B112="",B112=-999),"",B112*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D112" s="26">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E112" s="28">
+        <f>IF(OR(D112="",D112=-999),"",D112+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="113" ht="15" customHeight="1">
-      <c r="A113" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B113" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C113" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D113" s="27">
-        <f>IF(OR(B113="",B113=-999),"",B113*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E113" s="28">
-        <f>IF(OR(C113="",C113=-999),"",C113+$D$4)</f>
+      <c r="A113" s="21">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B113" s="22">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C113" s="23">
+        <f>IF(OR(B113="",B113=-999),"",B113*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D113" s="22">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E113" s="24">
+        <f>IF(OR(D113="",D113=-999),"",D113+$E$2)</f>
         <v/>
       </c>
     </row>
     <row r="114" ht="15" customHeight="1">
-      <c r="A114" s="29">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-13)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-13)),"")</f>
-        <v/>
-      </c>
-      <c r="B114" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C114" s="30">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-13,MATCH($B$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="D114" s="31">
-        <f>IF(OR(B114="",B114=-999),"",B114*$D$3)</f>
-        <v/>
-      </c>
-      <c r="E114" s="32">
-        <f>IF(OR(C114="",C114=-999),"",C114+$D$4)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="115" ht="28" customHeight="1">
-      <c r="A115" s="5" t="inlineStr">
-        <is>
-          <t>↑ Formula rows cover 100 data points. For more rows: select A15:E114, copy, paste below. For very large datasets use Power Query (see Instructions).</t>
+      <c r="A114" s="25">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B114" s="26">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C114" s="27">
+        <f>IF(OR(B114="",B114=-999),"",B114*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D114" s="26">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E114" s="28">
+        <f>IF(OR(D114="",D114=-999),"",D114+$E$2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115" ht="15" customHeight="1">
+      <c r="A115" s="21">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B115" s="22">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C115" s="23">
+        <f>IF(OR(B115="",B115=-999),"",B115*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D115" s="22">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E115" s="24">
+        <f>IF(OR(D115="",D115=-999),"",D115+$E$2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116" ht="15" customHeight="1">
+      <c r="A116" s="25">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B116" s="26">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C116" s="27">
+        <f>IF(OR(B116="",B116=-999),"",B116*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D116" s="26">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E116" s="28">
+        <f>IF(OR(D116="",D116=-999),"",D116+$E$2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117" ht="15" customHeight="1">
+      <c r="A117" s="21">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B117" s="22">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C117" s="23">
+        <f>IF(OR(B117="",B117=-999),"",B117*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D117" s="22">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E117" s="24">
+        <f>IF(OR(D117="",D117=-999),"",D117+$E$2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118" ht="15" customHeight="1">
+      <c r="A118" s="25">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B118" s="26">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C118" s="27">
+        <f>IF(OR(B118="",B118=-999),"",B118*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D118" s="26">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E118" s="28">
+        <f>IF(OR(D118="",D118=-999),"",D118+$E$2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119" ht="15" customHeight="1">
+      <c r="A119" s="21">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B119" s="22">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C119" s="23">
+        <f>IF(OR(B119="",B119=-999),"",B119*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D119" s="22">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E119" s="24">
+        <f>IF(OR(D119="",D119=-999),"",D119+$E$2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120" ht="15" customHeight="1">
+      <c r="A120" s="25">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B120" s="26">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C120" s="27">
+        <f>IF(OR(B120="",B120=-999),"",B120*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D120" s="26">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E120" s="28">
+        <f>IF(OR(D120="",D120=-999),"",D120+$E$2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121" ht="15" customHeight="1">
+      <c r="A121" s="21">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B121" s="22">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C121" s="23">
+        <f>IF(OR(B121="",B121=-999),"",B121*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D121" s="22">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E121" s="24">
+        <f>IF(OR(D121="",D121=-999),"",D121+$E$2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122" ht="15" customHeight="1">
+      <c r="A122" s="25">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B122" s="26">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C122" s="27">
+        <f>IF(OR(B122="",B122=-999),"",B122*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D122" s="26">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E122" s="28">
+        <f>IF(OR(D122="",D122=-999),"",D122+$E$2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123" ht="15" customHeight="1">
+      <c r="A123" s="21">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B123" s="22">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C123" s="23">
+        <f>IF(OR(B123="",B123=-999),"",B123*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D123" s="22">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E123" s="24">
+        <f>IF(OR(D123="",D123=-999),"",D123+$E$2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="124" ht="15" customHeight="1">
+      <c r="A124" s="25">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <v/>
+      </c>
+      <c r="B124" s="26">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C124" s="27">
+        <f>IF(OR(B124="",B124=-999),"",B124*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D124" s="26">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E124" s="28">
+        <f>IF(OR(D124="",D124=-999),"",D124+$E$2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125" ht="24" customHeight="1">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t>↑ Formulas cover 100 rows. For more data: select A25:E124 and copy-paste downward. For very large datasets use Power Query — see Instructions sheet.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A115:F115"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="A13:F13"/>
+  <mergeCells count="38">
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A125:E125"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="A19:B19"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="A9:B9"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="B3" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Invalid Flow" error="Please select a flow name from the list." type="list">
+  <conditionalFormatting sqref="A5:B20">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$A5=$B$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D5:E20">
+    <cfRule type="expression" priority="2" dxfId="1">
+      <formula>$D5=$E$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation sqref="B3" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Unknown Flow" error="Select a name from the Raw Flow Data headers." type="list">
       <formula1>'Raw Flow Data'!$B$1:$GR$1</formula1>
+    </dataValidation>
+    <dataValidation sqref="E3" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Unknown Pressure" error="Select a name from the Raw Pressure Data headers." type="list">
+      <formula1>'Raw Pressure Data'!$B$1:$GR$1</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -6630,7 +6811,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Flow Name</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -6642,7 +6823,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Data is appended here each time you run the SaveToMOD macro (history is preserved — rows are never overwritten).</t>
+          <t>Rows are appended here each time you run SaveToMOD. History is preserved — existing rows are never overwritten.</t>
         </is>
       </c>
     </row>
@@ -6676,7 +6857,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Flow Name</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -6688,7 +6869,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Data is appended here each time you run the SaveToMOD macro (history is preserved — rows are never overwritten).</t>
+          <t>Rows are appended here each time you run SaveToMOD. History is preserved — existing rows are never overwritten.</t>
         </is>
       </c>
     </row>
@@ -6706,658 +6887,490 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A95"/>
+  <dimension ref="A1:A65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="110" customWidth="1" min="1" max="1"/>
+    <col width="115" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="33" t="inlineStr">
-        <is>
-          <t>Flow &amp; Pressure Dashboard — Instructions &amp; Setup Guide</t>
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Flow &amp; Pressure Dashboard — Instructions</t>
         </is>
       </c>
     </row>
     <row r="2" ht="8" customHeight="1"/>
     <row r="3" ht="26" customHeight="1">
-      <c r="A3" s="34" t="inlineStr">
-        <is>
-          <t>1.  QUICK START  (Formula-Based — works immediately, no setup needed)</t>
+      <c r="A3" s="29" t="inlineStr">
+        <is>
+          <t>1.  QUICK START  (works immediately — no setup needed)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="17" customHeight="1">
-      <c r="A4" s="35" t="inlineStr">
-        <is>
-          <t>Step 1:  Go to the 'Raw Flow Data' sheet.  Delete the sample rows (keep Row 1 headers).  Paste your flow data from Row 2 onwards.</t>
+      <c r="A4" s="30" t="inlineStr">
+        <is>
+          <t>Step 1:  Paste your flow data into 'Raw Flow Data' (delete sample rows, keep Row 1 headers).</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="35" t="inlineStr">
-        <is>
-          <t>Step 2:  Go to the 'Raw Pressure Data' sheet and do the same with your pressure data.</t>
+      <c r="A5" s="30" t="inlineStr">
+        <is>
+          <t>Step 2:  Paste your pressure data into 'Raw Pressure Data' (same format).</t>
         </is>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="35" t="inlineStr">
-        <is>
-          <t>Step 3:  Go to the 'Dashboard' sheet.  Click cell B3 and pick a flow from the dropdown.</t>
+      <c r="A6" s="30" t="inlineStr">
+        <is>
+          <t>Step 3:  Go to the Dashboard sheet.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="35" t="inlineStr">
-        <is>
-          <t>Step 4:  Adjust 'Flow Scaling Factor' (cell D3) and 'Pressure Offset' (cell D4) as needed.</t>
+      <c r="A7" s="30" t="inlineStr">
+        <is>
+          <t>Step 4:  Use the 'Select Flow ▼' dropdown (cell B3) to pick a flow.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="35" t="inlineStr">
-        <is>
-          <t>Step 5:  The formula table (rows 15 onwards) and chart update automatically.</t>
+      <c r="A8" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">         The selected flow is highlighted in the list on the left.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="35" t="inlineStr">
-        <is>
-          <t>Note:    The formula table covers 100 rows. For more data rows, select A15:E114 and copy-paste downward.</t>
+      <c r="A9" s="30" t="inlineStr">
+        <is>
+          <t>Step 5:  Use the 'Select Pressure ▼' dropdown (cell E3) to pick a pressure.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="35" t="inlineStr">
-        <is>
-          <t>Note:    After pasting your own flow names, right-click cell B3 → Data Validation → update the</t>
+      <c r="A10" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">         The selected pressure is highlighted in the list on the right.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         Source range to match your column headers (e.g. 'Raw Flow Data'!$B$1:$BZ$1).</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="8" customHeight="1"/>
-    <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="36" t="inlineStr">
-        <is>
-          <t>2.  POWER QUERY SETUP  (recommended for large datasets)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="35" t="inlineStr">
-        <is>
-          <t>Power Query loads and transforms your raw data so PivotTables and charts always reflect the latest paste.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="8" customHeight="1"/>
-    <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="37" t="inlineStr">
-        <is>
-          <t>2a.  Load the Flow data query</t>
+      <c r="A11" s="30" t="inlineStr">
+        <is>
+          <t>Step 6:  Adjust 'Flow Scaling Factor' (B2) and 'Pressure Offset' (E2) if needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="17" customHeight="1">
+      <c r="A12" s="30" t="inlineStr">
+        <is>
+          <t>Step 7:  The chart (right side) and formula table (below) update instantly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="17" customHeight="1">
+      <c r="A13" s="30" t="inlineStr">
+        <is>
+          <t>Step 8:  When satisfied, run the SaveToMOD macro to store the adjusted data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="30" t="inlineStr"/>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="30" t="inlineStr">
+        <is>
+          <t>NOTE:  After pasting your own data, right-click cell B3 → Data Validation → update</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="17" customHeight="1">
+      <c r="A16" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       Source to cover your column range, e.g.  'Raw Flow Data'!$B$1:$BZ$1</t>
         </is>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
-      <c r="A17" s="38" t="inlineStr">
-        <is>
-          <t>1. Go to the 'Raw Flow Data' sheet and click anywhere inside the table.</t>
+      <c r="A17" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       Do the same for E3 using 'Raw Pressure Data'.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="17" customHeight="1">
-      <c r="A18" s="38" t="inlineStr">
-        <is>
-          <t>2. Data tab → Get Data → From Table/Range.  Power Query Editor opens.</t>
-        </is>
-      </c>
+      <c r="A18" s="30" t="inlineStr"/>
     </row>
     <row r="19" ht="17" customHeight="1">
-      <c r="A19" s="38" t="inlineStr">
-        <is>
-          <t>3. In Power Query Editor:  Home → Unpivot Other Columns  (select the Date column first, then Unpivot).</t>
+      <c r="A19" s="30" t="inlineStr">
+        <is>
+          <t>NOTE:  The formula table covers 100 rows. For longer datasets, select A25:E124</t>
         </is>
       </c>
     </row>
     <row r="20" ht="17" customHeight="1">
-      <c r="A20" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   This converts wide format (one column per flow) into long format: Date | Flow Name | Value.</t>
+      <c r="A20" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       and copy-paste downward as far as needed.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="17" customHeight="1">
-      <c r="A21" s="38" t="inlineStr">
-        <is>
-          <t>4. Rename the columns:  'Attribute' → 'Flow Name',  'Value' → 'Flow Value'.</t>
-        </is>
-      </c>
+      <c r="A21" s="30" t="inlineStr"/>
     </row>
     <row r="22" ht="17" customHeight="1">
-      <c r="A22" s="38" t="inlineStr">
-        <is>
-          <t>5. Home → Close &amp; Load To…  →  'Only Create Connection'  (tick 'Add to Data Model' if you like).</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="17" customHeight="1">
-      <c r="A23" s="38" t="inlineStr">
-        <is>
-          <t>6. Name the query  FlowLong.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="8" customHeight="1"/>
-    <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="37" t="inlineStr">
-        <is>
-          <t>2b.  Load the Pressure data query  (same steps)</t>
+      <c r="A22" s="30" t="inlineStr">
+        <is>
+          <t>NOTE:  -999 values are treated as no-data and are excluded from all calculations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="8" customHeight="1"/>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="31" t="inlineStr">
+        <is>
+          <t>2.  POWER QUERY SETUP  (optional — recommended for very large datasets)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="17" customHeight="1">
+      <c r="A25" s="30" t="inlineStr">
+        <is>
+          <t>The Raw data sheets are already set up as Excel Tables (FlowData, PressureData).</t>
         </is>
       </c>
     </row>
     <row r="26" ht="17" customHeight="1">
-      <c r="A26" s="38" t="inlineStr">
-        <is>
-          <t>1. Go to the 'Raw Pressure Data' sheet and repeat steps 1-5 above.</t>
+      <c r="A26" s="30" t="inlineStr">
+        <is>
+          <t>Power Query can load these tables, unpivot them, and merge them for use in PivotTables.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="17" customHeight="1">
-      <c r="A27" s="38" t="inlineStr">
-        <is>
-          <t>2. Rename columns:  'Attribute' → 'Flow Name',  'Value' → 'Pressure Value'.</t>
-        </is>
-      </c>
+      <c r="A27" s="30" t="inlineStr"/>
     </row>
     <row r="28" ht="17" customHeight="1">
-      <c r="A28" s="38" t="inlineStr">
-        <is>
-          <t>3. Name the query  PressureLong.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="8" customHeight="1"/>
-    <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="37" t="inlineStr">
-        <is>
-          <t>2c.  Load the Parameters table  (scaling factor and offset)</t>
+      <c r="A28" s="30" t="inlineStr">
+        <is>
+          <t>Step 1:  Data tab → Get Data → From Table/Range → select the FlowData table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="17" customHeight="1">
+      <c r="A29" s="30" t="inlineStr">
+        <is>
+          <t>Step 2:  In Power Query Editor: select the Date column, then Home → Unpivot Other Columns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="17" customHeight="1">
+      <c r="A30" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">         Rename 'Attribute' → 'Flow Name',  'Value' → 'Flow Value'.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="17" customHeight="1">
-      <c r="A31" s="38" t="inlineStr">
-        <is>
-          <t>1. Go to the 'Dashboard' sheet and click anywhere inside the orange Parameters table (C9:E11).</t>
+      <c r="A31" s="30" t="inlineStr">
+        <is>
+          <t>Step 3:  Close &amp; Load To… → Only Create Connection.  Name the query  FlowLong.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="17" customHeight="1">
-      <c r="A32" s="38" t="inlineStr">
-        <is>
-          <t>2. Data tab → Get Data → From Table/Range.</t>
+      <c r="A32" s="30" t="inlineStr">
+        <is>
+          <t>Step 4:  Repeat for PressureData.  Name the query  PressureLong.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="17" customHeight="1">
-      <c r="A33" s="38" t="inlineStr">
-        <is>
-          <t>3. No transformations needed — just click  Close &amp; Load To… → Only Create Connection.</t>
+      <c r="A33" s="30" t="inlineStr">
+        <is>
+          <t>Step 5:  Merge the two queries on Date + Name to get a combined table.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="17" customHeight="1">
-      <c r="A34" s="38" t="inlineStr">
-        <is>
-          <t>4. Name the query  Parameters.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="8" customHeight="1"/>
-    <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="37" t="inlineStr">
-        <is>
-          <t>2d.  Merge queries into one combined table</t>
+      <c r="A34" s="30" t="inlineStr">
+        <is>
+          <t>Step 6:  Add calculated columns:  Flow Adjusted = [Flow Value] × scaling_factor</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="17" customHeight="1">
+      <c r="A35" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                  Pressure Adjusted = [Pressure Value] + offset</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="17" customHeight="1">
+      <c r="A36" s="30" t="inlineStr">
+        <is>
+          <t>Step 7:  Load the merged query to a sheet and build a PivotTable + Slicer on top of it.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="17" customHeight="1">
-      <c r="A37" s="38" t="inlineStr">
-        <is>
-          <t>1. Data tab → Get Data → Combine Queries → Merge.</t>
-        </is>
-      </c>
+      <c r="A37" s="30" t="inlineStr"/>
     </row>
     <row r="38" ht="17" customHeight="1">
-      <c r="A38" s="38" t="inlineStr">
-        <is>
-          <t>2. Select FlowLong as the left table; PressureLong as the right table.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="17" customHeight="1">
-      <c r="A39" s="38" t="inlineStr">
-        <is>
-          <t>3. Match on:  Date  AND  Flow Name  (hold Ctrl to select both columns).</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="17" customHeight="1">
-      <c r="A40" s="38" t="inlineStr">
-        <is>
-          <t>4. Expand the merged column to include 'Pressure Value'.</t>
+      <c r="A38" s="30" t="inlineStr">
+        <is>
+          <t>After pasting new data:  Data tab → Refresh All  (Ctrl+Alt+F5).</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="8" customHeight="1"/>
+    <row r="40" ht="26" customHeight="1">
+      <c r="A40" s="32" t="inlineStr">
+        <is>
+          <t>3.  PIVOTTABLE + SLICER  (optional — for interactive multi-flow comparison)</t>
         </is>
       </c>
     </row>
     <row r="41" ht="17" customHeight="1">
-      <c r="A41" s="38" t="inlineStr">
-        <is>
-          <t>5. Add a custom column for Flow Adjusted:</t>
+      <c r="A41" s="30" t="inlineStr">
+        <is>
+          <t>Once the Power Query merged table is loaded to a sheet:</t>
         </is>
       </c>
     </row>
     <row r="42" ht="17" customHeight="1">
-      <c r="A42" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   = if [Flow Value] = -999 then null else [Flow Value] * Parameters{[Parameter="Flow Scaling Factor"]}[Value]</t>
+      <c r="A42" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Insert → PivotTable</t>
         </is>
       </c>
     </row>
     <row r="43" ht="17" customHeight="1">
-      <c r="A43" s="38" t="inlineStr">
-        <is>
-          <t>6. Add a custom column for Pressure Adjusted:</t>
+      <c r="A43" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Rows: Date    Values: Flow Adjusted, Pressure Adjusted</t>
         </is>
       </c>
     </row>
     <row r="44" ht="17" customHeight="1">
-      <c r="A44" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   = if [Pressure Value] = -999 then null else [Pressure Value] + Parameters{[Parameter="Pressure Offset"]}[Value]</t>
+      <c r="A44" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • PivotTable Analyze → Insert Slicer → tick 'Flow Name' → OK</t>
         </is>
       </c>
     </row>
     <row r="45" ht="17" customHeight="1">
-      <c r="A45" s="38" t="inlineStr">
-        <is>
-          <t>7. Home → Close &amp; Load To… → Table  (load to a new sheet, e.g. 'PQ Output').</t>
+      <c r="A45" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Click a flow name in the Slicer to filter instantly</t>
         </is>
       </c>
     </row>
     <row r="46" ht="17" customHeight="1">
-      <c r="A46" s="38" t="inlineStr">
-        <is>
-          <t>8. Name the query  CombinedAdjusted.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="17" customHeight="1">
-      <c r="A47" s="38" t="inlineStr"/>
-    </row>
-    <row r="48" ht="17" customHeight="1">
-      <c r="A48" s="38" t="inlineStr">
-        <is>
-          <t>To refresh after pasting new data:  Data tab → Refresh All  (or Ctrl+Alt+F5).</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="8" customHeight="1"/>
-    <row r="50" ht="26" customHeight="1">
-      <c r="A50" s="39" t="inlineStr">
-        <is>
-          <t>3.  PIVOTTABLE + SLICER SETUP  (interactive filtering)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="18" customHeight="1">
+      <c r="A46" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Insert → PivotChart → Line → add Secondary Axis to the Pressure series</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="8" customHeight="1"/>
+    <row r="48" ht="26" customHeight="1">
+      <c r="A48" s="33" t="inlineStr">
+        <is>
+          <t>4.  VBA SAVE BUTTON  (paste this into a Module — Alt+F11 → Insert → Module)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="17" customHeight="1">
+      <c r="A49" s="34" t="inlineStr">
+        <is>
+          <t>Assign the macro to a button on the Dashboard: Developer tab → Insert → Button (Form Control).</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="8" customHeight="1"/>
+    <row r="51" ht="17" customHeight="1">
       <c r="A51" s="35" t="inlineStr">
         <is>
-          <t>Once you have the CombinedAdjusted Power Query output loaded to a sheet, follow these steps:</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="8" customHeight="1"/>
-    <row r="53" ht="16" customHeight="1">
-      <c r="A53" s="37" t="inlineStr">
-        <is>
-          <t>3a.  Create the PivotTable</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="17" customHeight="1">
-      <c r="A54" s="38" t="inlineStr">
-        <is>
-          <t>1. Click anywhere in the CombinedAdjusted table on the 'PQ Output' sheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="17" customHeight="1">
-      <c r="A55" s="38" t="inlineStr">
-        <is>
-          <t>2. Insert → PivotTable → New Worksheet (or Existing Worksheet).</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="17" customHeight="1">
-      <c r="A56" s="38" t="inlineStr">
-        <is>
-          <t>3. In the PivotTable Field List:</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="17" customHeight="1">
-      <c r="A57" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   • Drag 'Date' to ROWS.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="17" customHeight="1">
-      <c r="A58" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   • Drag 'Flow Adjusted' to VALUES  (set to Sum or Average).</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="17" customHeight="1">
-      <c r="A59" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   • Drag 'Pressure Adjusted' to VALUES  (set to Sum or Average).</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="17" customHeight="1">
-      <c r="A60" s="38" t="inlineStr">
-        <is>
-          <t>4. Right-click a date cell → Group → by Hours or Minutes to control time grouping.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="8" customHeight="1"/>
-    <row r="62" ht="16" customHeight="1">
-      <c r="A62" s="37" t="inlineStr">
-        <is>
-          <t>3b.  Add a Flow Name Slicer</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="17" customHeight="1">
-      <c r="A63" s="38" t="inlineStr">
-        <is>
-          <t>1. Click anywhere in the PivotTable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="17" customHeight="1">
-      <c r="A64" s="38" t="inlineStr">
-        <is>
-          <t>2. PivotTable Analyze tab → Insert Slicer.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="17" customHeight="1">
-      <c r="A65" s="38" t="inlineStr">
-        <is>
-          <t>3. Tick 'Flow Name' → OK.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="17" customHeight="1">
-      <c r="A66" s="38" t="inlineStr">
-        <is>
-          <t>4. Click a flow name in the Slicer to filter the PivotTable (and chart) to that flow.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="17" customHeight="1">
-      <c r="A67" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Hold Ctrl to select multiple flows.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="8" customHeight="1"/>
-    <row r="69" ht="16" customHeight="1">
-      <c r="A69" s="37" t="inlineStr">
-        <is>
-          <t>3c.  Create a PivotChart</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="17" customHeight="1">
-      <c r="A70" s="38" t="inlineStr">
-        <is>
-          <t>1. Click anywhere in the PivotTable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="17" customHeight="1">
-      <c r="A71" s="38" t="inlineStr">
-        <is>
-          <t>2. PivotTable Analyze tab → PivotChart → Line → Line with Markers.</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="17" customHeight="1">
-      <c r="A72" s="38" t="inlineStr">
-        <is>
-          <t>3. To add a secondary axis for Pressure:</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="17" customHeight="1">
-      <c r="A73" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Right-click the Pressure Adjusted series → Format Data Series → Secondary Axis.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="17" customHeight="1">
-      <c r="A74" s="38" t="inlineStr">
-        <is>
-          <t>4. The chart updates automatically when you click a flow in the Slicer.</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="8" customHeight="1"/>
-    <row r="76" ht="26" customHeight="1">
-      <c r="A76" s="40" t="inlineStr">
-        <is>
-          <t>4.  VBA SAVE BUTTON CODE  (paste this yourself)</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="18" customHeight="1">
-      <c r="A77" s="35" t="inlineStr">
-        <is>
-          <t>Press Alt+F11 to open the VBA editor.  Insert → Module, then paste the code below.</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="8" customHeight="1"/>
-    <row r="79" ht="18" customHeight="1">
-      <c r="A79" s="41" t="inlineStr">
-        <is>
-          <t>' ─────────────────────────────────────────────────────────────────────────────
-' SaveToMOD  —  copies the current adjusted table on Dashboard to the MOD tabs
-' Assign this macro to a button on the Dashboard sheet.
-' ─────────────────────────────────────────────────────────────────────────────
+          <t>' ═══════════════════════════════════════════════════════════════════════════
+' SaveToMOD  —  appends current adjusted data to MOD Flow and MOD Pressure
+' Reads:  B3 (selected flow), E3 (selected pressure), B2 (scaling), E2 (offset)
+'         Data table rows 25 onwards, columns A-E
+' ═══════════════════════════════════════════════════════════════════════════
 Sub SaveToMOD()
-    Dim wsDash      As Worksheet
-    Dim wsModFlow   As Worksheet
-    Dim wsModPres   As Worksheet
+    Dim wsDash    As Worksheet
+    Dim wsModFlow As Worksheet
+    Dim wsModPres As Worksheet
+    On Error Resume Next
     Set wsDash    = Worksheets("Dashboard")
     Set wsModFlow = Worksheets("MOD Flow")
     Set wsModPres = Worksheets("MOD Pressure")
-    ' ── Validate ──────────────────────────────────────────────────────────────
+    On Error GoTo 0
+    If wsDash Is Nothing Or wsModFlow Is Nothing Or wsModPres Is Nothing Then
+        MsgBox "Could not find Dashboard, MOD Flow, or MOD Pressure sheet.", _
+               vbCritical, "Sheet Missing"
+        Exit Sub
+    End If
+    ' ── Validate selections ──────────────────────────────────────────────────
     Dim flowName As String
+    Dim presName As String
     flowName = Trim(wsDash.Range("B3").Value)
+    presName = Trim(wsDash.Range("E3").Value)
     If flowName = "" Then
-        MsgBox "Please select a flow from the dropdown (cell B3) before saving.", _
+        MsgBox "Please select a Flow from the dropdown (cell B3).", _
                vbExclamation, "No Flow Selected"
         Exit Sub
     End If
-    ' ── Find the last data row on Dashboard ──────────────────────────────────
-    Const DATA_START As Long = 15        ' first formula row
+    If presName = "" Then
+        MsgBox "Please select a Pressure from the dropdown (cell E3).", _
+               vbExclamation, "No Pressure Selected"
+        Exit Sub
+    End If
+    ' ── Find last row with data ──────────────────────────────────────────────
+    Const DATA_START As Long = 25
     Dim lastRow As Long
     lastRow = wsDash.Cells(wsDash.Rows.Count, "A").End(xlUp).Row
     If lastRow &lt; DATA_START Then
-        MsgBox "No data found in the formula table (rows 15 onwards).", _
+        MsgBox "No data found in the formula table (rows 25 onwards).", _
                vbExclamation, "No Data"
         Exit Sub
     End If
-    ' ── Find next empty row in each MOD tab ──────────────────────────────────
-    Dim nextFlow As Long
-    Dim nextPres As Long
-    nextFlow = wsModFlow.Cells(wsModFlow.Rows.Count, "A").End(xlUp).Row + 1
-    nextPres = wsModPres.Cells(wsModPres.Rows.Count, "A").End(xlUp).Row + 1
-    If nextFlow &lt; 3 Then nextFlow = 3    ' skip header + info rows
-    If nextPres &lt; 3 Then nextPres = 3
-    ' ── Disable screen updates for speed ─────────────────────────────────────
     Application.ScreenUpdating = False
-    Dim i           As Long
-    Dim savedRows   As Long
-    savedRows = 0
+    ' ── Next empty row in each MOD tab (skip header + info row) ─────────────
+    Dim nFlow As Long
+    Dim nPres As Long
+    nFlow = wsModFlow.Cells(wsModFlow.Rows.Count, "A").End(xlUp).Row + 1
+    nPres = wsModPres.Cells(wsModPres.Rows.Count, "A").End(xlUp).Row + 1
+    If nFlow &lt; 3 Then nFlow = 3
+    If nPres &lt; 3 Then nPres = 3
+    Dim saved As Long
+    Dim i As Long
     For i = DATA_START To lastRow
-        Dim dateVal     As Variant
-        Dim flowAdj     As Variant
-        Dim presAdj     As Variant
-        dateVal = wsDash.Cells(i, "A").Value
-        flowAdj = wsDash.Cells(i, "D").Value   ' Flow Adjusted
-        presAdj = wsDash.Cells(i, "E").Value   ' Pressure Adjusted
-        ' Skip rows where date or both values are empty
-        If dateVal = "" Or (flowAdj = "" And presAdj = "") Then GoTo NextRow
-        ' Write to MOD Flow
+        Dim dtVal     As Variant
+        Dim flowAdj   As Variant
+        Dim presAdj   As Variant
+        dtVal   = wsDash.Cells(i, "A").Value   ' Date
+        flowAdj = wsDash.Cells(i, "C").Value   ' Flow Adjusted   (col C)
+        presAdj = wsDash.Cells(i, "E").Value   ' Pressure Adjusted (col E)
+        If dtVal = "" Then GoTo Skip
         If flowAdj &lt;&gt; "" Then
-            wsModFlow.Cells(nextFlow, "A").Value = dateVal
-            wsModFlow.Cells(nextFlow, "A").NumberFormat = "DD/MM/YYYY HH:MM"
-            wsModFlow.Cells(nextFlow, "B").Value = flowName
-            wsModFlow.Cells(nextFlow, "C").Value = flowAdj
-            wsModFlow.Cells(nextFlow, "C").NumberFormat = "0.000"
-            nextFlow = nextFlow + 1
+            wsModFlow.Cells(nFlow, "A").Value         = dtVal
+            wsModFlow.Cells(nFlow, "A").NumberFormat  = "DD/MM/YYYY HH:MM"
+            wsModFlow.Cells(nFlow, "B").Value         = flowName
+            wsModFlow.Cells(nFlow, "C").Value         = flowAdj
+            wsModFlow.Cells(nFlow, "C").NumberFormat  = "0.000"
+            nFlow = nFlow + 1
         End If
-        ' Write to MOD Pressure
         If presAdj &lt;&gt; "" Then
-            wsModPres.Cells(nextPres, "A").Value = dateVal
-            wsModPres.Cells(nextPres, "A").NumberFormat = "DD/MM/YYYY HH:MM"
-            wsModPres.Cells(nextPres, "B").Value = flowName
-            wsModPres.Cells(nextPres, "C").Value = presAdj
-            wsModPres.Cells(nextPres, "C").NumberFormat = "0.000"
-            nextPres = nextPres + 1
+            wsModPres.Cells(nPres, "A").Value         = dtVal
+            wsModPres.Cells(nPres, "A").NumberFormat  = "DD/MM/YYYY HH:MM"
+            wsModPres.Cells(nPres, "B").Value         = presName
+            wsModPres.Cells(nPres, "C").Value         = presAdj
+            wsModPres.Cells(nPres, "C").NumberFormat  = "0.000"
+            nPres = nPres + 1
         End If
-        savedRows = savedRows + 1
-NextRow:
+        saved = saved + 1
+Skip:
     Next i
     Application.ScreenUpdating = True
-    If savedRows = 0 Then
-        MsgBox "No data rows were saved. Make sure the formula table has data.", _
+    If saved = 0 Then
+        MsgBox "No data rows were saved — check the formula table has values.", _
                vbExclamation, "Nothing Saved"
     Else
-        MsgBox "Saved " &amp; savedRows &amp; " rows for flow: " &amp; flowName &amp; Chr(10) &amp; _
-               "  → MOD Flow       (" &amp; (nextFlow - 3) &amp; " rows total)" &amp; Chr(10) &amp; _
-               "  → MOD Pressure   (" &amp; (nextPres - 3) &amp; " rows total)", _
+        MsgBox "Saved " &amp; saved &amp; " rows." &amp; Chr(10) &amp; Chr(10) &amp; _
+               "  Flow:     " &amp; flowName &amp; Chr(10) &amp; _
+               "  Pressure: " &amp; presName, _
                vbInformation, "Save Complete"
     End If
 End Sub</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="8" customHeight="1"/>
-    <row r="81" ht="18" customHeight="1">
-      <c r="A81" s="42" t="inlineStr">
-        <is>
-          <t>To add a button:  Developer tab → Insert → Button (Form Control) → draw on Dashboard → assign macro SaveToMOD.</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="18" customHeight="1">
-      <c r="A82" s="42" t="inlineStr">
-        <is>
-          <t>If the Developer tab is not visible:  File → Options → Customise Ribbon → tick Developer.</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="8" customHeight="1"/>
-    <row r="84" ht="26" customHeight="1">
-      <c r="A84" s="43" t="inlineStr">
+    <row r="52" ht="8" customHeight="1"/>
+    <row r="53" ht="26" customHeight="1">
+      <c r="A53" s="36" t="inlineStr">
         <is>
           <t>5.  DATA FORMAT REFERENCE</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="17" customHeight="1">
-      <c r="A85" s="35" t="inlineStr">
+    <row r="54" ht="17" customHeight="1">
+      <c r="A54" s="30" t="inlineStr">
         <is>
           <t>Both Raw Data sheets expect this wide format:</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="17" customHeight="1">
-      <c r="A86" s="35" t="inlineStr"/>
-    </row>
-    <row r="87" ht="17" customHeight="1">
-      <c r="A87" s="35" t="inlineStr">
+    <row r="55" ht="17" customHeight="1">
+      <c r="A55" s="30" t="inlineStr"/>
+    </row>
+    <row r="56" ht="17" customHeight="1">
+      <c r="A56" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">    Date               | AL012       | AL013       | AL014       | ...  </t>
         </is>
       </c>
     </row>
-    <row r="88" ht="17" customHeight="1">
-      <c r="A88" s="35" t="inlineStr">
+    <row r="57" ht="17" customHeight="1">
+      <c r="A57" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">    12/01/2026 00:00   | 3.168205    | 2.204250    | 2.665153    | ...  </t>
         </is>
       </c>
     </row>
-    <row r="89" ht="17" customHeight="1">
-      <c r="A89" s="35" t="inlineStr">
+    <row r="58" ht="17" customHeight="1">
+      <c r="A58" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">    12/01/2026 00:15   | 3.190769    | 2.225250    | 2.681334    | ...  </t>
         </is>
       </c>
     </row>
-    <row r="90" ht="17" customHeight="1">
-      <c r="A90" s="35" t="inlineStr"/>
-    </row>
-    <row r="91" ht="17" customHeight="1">
-      <c r="A91" s="35" t="inlineStr">
-        <is>
-          <t>• Column A must be a Date/Time value (not text).</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="17" customHeight="1">
-      <c r="A92" s="35" t="inlineStr">
-        <is>
-          <t>• Flow/pressure names can be any combination of letters and numbers (AL012, AM005, AF037, etc.).</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="17" customHeight="1">
-      <c r="A93" s="35" t="inlineStr">
-        <is>
-          <t>• Use -999 to represent missing / no-data values — they are excluded from all calculations.</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="17" customHeight="1">
-      <c r="A94" s="35" t="inlineStr">
-        <is>
-          <t>• Data can be any length (months of 15-minute intervals = thousands of rows).</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="17" customHeight="1">
-      <c r="A95" s="35" t="inlineStr">
-        <is>
-          <t>• Both sheets must use the same flow/pressure names (column headers must match).</t>
+    <row r="59" ht="17" customHeight="1">
+      <c r="A59" s="30" t="inlineStr"/>
+    </row>
+    <row r="60" ht="17" customHeight="1">
+      <c r="A60" s="30" t="inlineStr">
+        <is>
+          <t>• Column A must contain a proper Date/Time value (not text).</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="17" customHeight="1">
+      <c r="A61" s="30" t="inlineStr">
+        <is>
+          <t>• Flow and pressure column names can be any mix of letters and numbers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="17" customHeight="1">
+      <c r="A62" s="30" t="inlineStr">
+        <is>
+          <t>• The flow names in Raw Flow Data and the pressure names in Raw Pressure Data</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="17" customHeight="1">
+      <c r="A63" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  do NOT need to match — you select each independently on the Dashboard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="17" customHeight="1">
+      <c r="A64" s="30" t="inlineStr">
+        <is>
+          <t>• Use -999 for missing/no-data values — they are excluded from all calculations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="17" customHeight="1">
+      <c r="A65" s="30" t="inlineStr">
+        <is>
+          <t>• Data can be any length: months of 15-minute data = thousands of rows.</t>
         </is>
       </c>
     </row>

--- a/Flow_Pressure_Dashboard.xlsx
+++ b/Flow_Pressure_Dashboard.xlsx
@@ -423,162 +423,165 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
-  <chart>
-    <title>
-      <tx>
-        <rich>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:style val="10"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
             <a:r>
               <a:t>Flow &amp; Pressure Analysis</a:t>
             </a:r>
           </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Dashboard'!C24</f>
-            </strRef>
-          </tx>
-          <spPr>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Dashboard!$C$24</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
             <a:ln w="20000">
               <a:solidFill>
                 <a:srgbClr val="2E75B6"/>
               </a:solidFill>
-              <a:prstDash val="solid"/>
             </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Dashboard'!$A$25:$A$124</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Dashboard'!$C$25:$C$124</f>
-            </numRef>
-          </val>
-        </ser>
-        <axId val="100"/>
-      </lineChart>
-      <lineChart>
-        <grouping val="standard"/>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'Dashboard'!E24</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Dashboard!$A$25:$A$124</c:f>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Dashboard!$C$25:$C$124</c:f>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="1001"/>
+        <c:axId val="1002"/>
+      </c:lineChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Dashboard!$E$24</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="20000">
+              <a:solidFill>
+                <a:srgbClr val="C55A11"/>
+              </a:solidFill>
             </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Dashboard'!$A$25:$A$124</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Dashboard'!$E$25:$E$124</f>
-            </numRef>
-          </val>
-        </ser>
-        <axId val="100"/>
-        <axId val="200"/>
-      </lineChart>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Dashboard!$A$25:$A$124</c:f>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Dashboard!$E$25:$E$124</c:f>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="1001"/>
+        <c:axId val="1003"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1001"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="m/d/yy" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:crossAx val="1002"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:title>
+          <c:tx>
+            <c:rich>
               <a:bodyPr/>
               <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
                 <a:r>
                   <a:t>Flow Adjusted</a:t>
                 </a:r>
               </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-      <valAx>
-        <axId val="200"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="r"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:crossAx val="1001"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1003"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="r"/>
+        <c:majorGridlines/>
+        <c:title>
+          <c:tx>
+            <c:rich>
               <a:bodyPr/>
               <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
                 <a:r>
                   <a:t>Pressure Adjusted</a:t>
                 </a:r>
               </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-        <crosses val="max"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:crosses val="max"/>
+        <c:crossAx val="1001"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+</c:chartSpace>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Flow_Pressure_Dashboard.xlsx
+++ b/Flow_Pressure_Dashboard.xlsx
@@ -424,13 +424,18 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
   <c:style val="10"/>
   <c:chart>
     <c:title>
       <c:tx>
         <c:rich>
           <a:bodyPr/>
+          <a:lstStyle/>
           <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
             <a:r>
               <a:t>Flow &amp; Pressure Analysis</a:t>
             </a:r>
@@ -441,6 +446,7 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
+      <c:layout/>
       <c:lineChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
@@ -462,6 +468,7 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:smooth val="0"/>
           <c:cat>
             <c:numRef>
               <c:f>Dashboard!$A$25:$A$124</c:f>
@@ -473,6 +480,10 @@
             </c:numRef>
           </c:val>
         </c:ser>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:smooth val="0"/>
         <c:axId val="1001"/>
         <c:axId val="1002"/>
       </c:lineChart>
@@ -497,6 +508,7 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:smooth val="0"/>
           <c:cat>
             <c:numRef>
               <c:f>Dashboard!$A$25:$A$124</c:f>
@@ -508,6 +520,10 @@
             </c:numRef>
           </c:val>
         </c:ser>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:smooth val="0"/>
         <c:axId val="1001"/>
         <c:axId val="1003"/>
       </c:lineChart>
@@ -519,9 +535,14 @@
         <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:numFmt formatCode="m/d/yy" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
         <c:crossAx val="1002"/>
+        <c:auto val="1"/>
+        <c:lblAlign val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="1002"/>
@@ -535,7 +556,11 @@
           <c:tx>
             <c:rich>
               <a:bodyPr/>
+              <a:lstStyle/>
               <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
                 <a:r>
                   <a:t>Flow Adjusted</a:t>
                 </a:r>
@@ -544,9 +569,13 @@
           </c:tx>
           <c:overlay val="0"/>
         </c:title>
-        <c:majorTickMark val="none"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
         <c:crossAx val="1001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
         <c:axId val="1003"/>
@@ -560,7 +589,11 @@
           <c:tx>
             <c:rich>
               <a:bodyPr/>
+              <a:lstStyle/>
               <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
                 <a:r>
                   <a:t>Pressure Adjusted</a:t>
                 </a:r>
@@ -569,17 +602,22 @@
           </c:tx>
           <c:overlay val="0"/>
         </c:title>
-        <c:majorTickMark val="none"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1001"/>
         <c:crosses val="max"/>
-        <c:crossAx val="1001"/>
+        <c:crossBetween val="between"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
+      <c:overlay val="0"/>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
 </c:chartSpace>
 </file>

--- a/Flow_Pressure_Dashboard.xlsx
+++ b/Flow_Pressure_Dashboard.xlsx
@@ -256,13 +256,13 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -455,7 +455,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Dashboard!$C$24</c:f>
+              <c:f>Dashboard!$C$26</c:f>
             </c:strRef>
           </c:tx>
           <c:spPr>
@@ -471,12 +471,188 @@
           <c:smooth val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>Dashboard!$A$25:$A$124</c:f>
+              <c:f>Dashboard!$A$27:$A$126</c:f>
+              <c:numCache>
+                <c:formatCode>m/d/yy h:mm</c:formatCode>
+                <c:ptCount val="28"/>
+                <c:pt idx="0">
+                  <c:v>46357.00000000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46357.01041667</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46357.02083333</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46357.03125000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46357.04166667</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46357.05208333</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46357.06250000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46357.07291667</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46357.08333333</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46357.09375000</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46357.10416667</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>46357.11458333</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>46357.12500000</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>46357.13541667</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>46357.14583333</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>46357.15625000</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>46357.16666667</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>46357.17708333</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>46357.18750000</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>46357.19791667</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>46357.20833333</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>46357.21875000</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>46357.22916667</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>46357.23958333</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>46357.25000000</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>46357.26041667</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>46357.27083333</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>46357.28125000</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Dashboard!$C$25:$C$124</c:f>
+              <c:f>Dashboard!$C$27:$C$126</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="28"/>
+                <c:pt idx="0">
+                  <c:v>3.168205</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.190769</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.21641</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.242051</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.265641</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.289231</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3.31282</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3.33641</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.361026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3.386667</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3.408205</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3.43282</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3.459487</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>3.483077</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3.509743</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3.53641</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3.557949</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3.582564</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3.608205</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>3.630769</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>3.655385</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>3.678974</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>3.700513</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>3.72</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>3.737436</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>3.744615</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>3.749743</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>3.746667</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -495,7 +671,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Dashboard!$E$24</c:f>
+              <c:f>Dashboard!$E$26</c:f>
             </c:strRef>
           </c:tx>
           <c:spPr>
@@ -511,12 +687,432 @@
           <c:smooth val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>Dashboard!$A$25:$A$124</c:f>
+              <c:f>Dashboard!$A$27:$A$126</c:f>
+              <c:numCache>
+                <c:formatCode>m/d/yy h:mm</c:formatCode>
+                <c:ptCount val="28"/>
+                <c:pt idx="0">
+                  <c:v>46357.00000000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46357.01041667</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46357.02083333</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46357.03125000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46357.04166667</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46357.05208333</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46357.06250000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46357.07291667</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46357.08333333</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46357.09375000</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46357.10416667</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>46357.11458333</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>46357.12500000</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>46357.13541667</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>46357.14583333</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>46357.15625000</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>46357.16666667</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>46357.17708333</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>46357.18750000</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>46357.19791667</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>46357.20833333</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>46357.21875000</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>46357.22916667</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>46357.23958333</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>46357.25000000</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>46357.26041667</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>46357.27083333</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>46357.28125000</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Dashboard!$E$25:$E$124</c:f>
+              <c:f>Dashboard!$E$27:$E$126</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="28"/>
+                <c:pt idx="0">
+                  <c:v>3.373159</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.395046</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.419918</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.444789</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.467672</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.490554</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3.513435</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3.536318</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.560195</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3.585067</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3.605959</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3.629835</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3.655702</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>3.678585</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3.704451</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3.730318</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3.751211</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3.775087</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3.799959</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>3.821846</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>3.845723</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>3.868605</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>3.889498</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>3.9084</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>3.925313</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>3.932277</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>3.937251</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>3.934267</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Dashboard!$G$26</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="20000">
+              <a:solidFill>
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:smooth val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>Dashboard!$A$27:$A$126</c:f>
+              <c:numCache>
+                <c:formatCode>m/d/yy h:mm</c:formatCode>
+                <c:ptCount val="28"/>
+                <c:pt idx="0">
+                  <c:v>46357.00000000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46357.01041667</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46357.02083333</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46357.03125000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46357.04166667</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46357.05208333</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46357.06250000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46357.07291667</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46357.08333333</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46357.09375000</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46357.10416667</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>46357.11458333</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>46357.12500000</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>46357.13541667</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>46357.14583333</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>46357.15625000</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>46357.16666667</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>46357.17708333</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>46357.18750000</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>46357.19791667</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>46357.20833333</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>46357.21875000</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>46357.22916667</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>46357.23958333</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>46357.25000000</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>46357.26041667</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>46357.27083333</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>46357.28125000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Dashboard!$G$27:$G$126</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="0"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Dashboard!$I$26</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="20000">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:smooth val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>Dashboard!$A$27:$A$126</c:f>
+              <c:numCache>
+                <c:formatCode>m/d/yy h:mm</c:formatCode>
+                <c:ptCount val="28"/>
+                <c:pt idx="0">
+                  <c:v>46357.00000000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46357.01041667</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46357.02083333</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46357.03125000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46357.04166667</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46357.05208333</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46357.06250000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46357.07291667</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46357.08333333</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46357.09375000</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46357.10416667</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>46357.11458333</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>46357.12500000</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>46357.13541667</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>46357.14583333</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>46357.15625000</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>46357.16666667</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>46357.17708333</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>46357.18750000</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>46357.19791667</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>46357.20833333</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>46357.21875000</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>46357.22916667</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>46357.23958333</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>46357.25000000</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>46357.26041667</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>46357.27083333</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>46357.28125000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Dashboard!$I$27:$I$126</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="0"/>
+              </c:numCache>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -534,7 +1130,7 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="m/d/yy" sourceLinked="1"/>
+        <c:numFmt formatCode="d/m/yy h:mm" sourceLinked="1"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -4224,7 +4820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F125"/>
+  <dimension ref="A1:I127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4232,7 +4828,10 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="2" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -4263,7 +4862,7 @@
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Select Flow  ▼</t>
+          <t>Select Flow  ▼  (blank = hide)</t>
         </is>
       </c>
       <c r="B3" s="11" t="inlineStr">
@@ -4273,7 +4872,7 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Select Pressure  ▼</t>
+          <t>Pressure 1  ▼</t>
         </is>
       </c>
       <c r="E3" s="13" t="inlineStr">
@@ -4282,334 +4881,326 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="20" customHeight="1">
+    <row r="4" ht="26" customHeight="1">
       <c r="A4" s="14" t="inlineStr">
         <is>
           <t>All Flows  (current selection highlighted)</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
-        <is>
-          <t>All Pressures  (current selection highlighted)</t>
-        </is>
-      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>Pressure 2  ▼  (optional)</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr"/>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>AL012</t>
         </is>
       </c>
-      <c r="B5" s="17" t="n"/>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="B5" s="16" t="n"/>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>Pressure 3  ▼  (optional)</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr"/>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>AL013</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="n"/>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>All Pressures  (highlighted = any of P1/P2/P3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>AL014</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="n"/>
+      <c r="D7" s="15" t="inlineStr">
         <is>
           <t>AL012</t>
         </is>
       </c>
-      <c r="E5" s="17" t="n"/>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="E7" s="16" t="n"/>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>AL023</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="n"/>
+      <c r="D8" s="15" t="inlineStr">
         <is>
           <t>AL013</t>
         </is>
       </c>
-      <c r="B6" s="17" t="n"/>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>AL013</t>
-        </is>
-      </c>
-      <c r="E6" s="17" t="n"/>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="E8" s="16" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>AL028</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="n"/>
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t>AL014</t>
         </is>
       </c>
-      <c r="B7" s="17" t="n"/>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>AL014</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="n"/>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="E9" s="16" t="n"/>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>AL029</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="n"/>
+      <c r="D10" s="15" t="inlineStr">
         <is>
           <t>AL023</t>
         </is>
       </c>
-      <c r="B8" s="17" t="n"/>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>AL023</t>
-        </is>
-      </c>
-      <c r="E8" s="17" t="n"/>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="E10" s="16" t="n"/>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>AL035</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="n"/>
+      <c r="D11" s="15" t="inlineStr">
         <is>
           <t>AL028</t>
         </is>
       </c>
-      <c r="B9" s="17" t="n"/>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>AL028</t>
-        </is>
-      </c>
-      <c r="E9" s="17" t="n"/>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="E11" s="16" t="n"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>AL036</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="n"/>
+      <c r="D12" s="15" t="inlineStr">
         <is>
           <t>AL029</t>
         </is>
       </c>
-      <c r="B10" s="17" t="n"/>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>AL029</t>
-        </is>
-      </c>
-      <c r="E10" s="17" t="n"/>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="E12" s="16" t="n"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>AL038</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="n"/>
+      <c r="D13" s="15" t="inlineStr">
         <is>
           <t>AL035</t>
         </is>
       </c>
-      <c r="B11" s="17" t="n"/>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>AL035</t>
-        </is>
-      </c>
-      <c r="E11" s="17" t="n"/>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="E13" s="16" t="n"/>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>AL063</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="n"/>
+      <c r="D14" s="15" t="inlineStr">
         <is>
           <t>AL036</t>
         </is>
       </c>
-      <c r="B12" s="17" t="n"/>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>AL036</t>
-        </is>
-      </c>
-      <c r="E12" s="17" t="n"/>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
+      <c r="E14" s="16" t="n"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>AM005</t>
+        </is>
+      </c>
+      <c r="B15" s="16" t="n"/>
+      <c r="D15" s="15" t="inlineStr">
         <is>
           <t>AL038</t>
         </is>
       </c>
-      <c r="B13" s="17" t="n"/>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>AL038</t>
-        </is>
-      </c>
-      <c r="E13" s="17" t="n"/>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
+      <c r="E15" s="16" t="n"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>AM014</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="n"/>
+      <c r="D16" s="15" t="inlineStr">
         <is>
           <t>AL063</t>
         </is>
       </c>
-      <c r="B14" s="17" t="n"/>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>AL063</t>
-        </is>
-      </c>
-      <c r="E14" s="17" t="n"/>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="16" t="inlineStr">
+      <c r="E16" s="16" t="n"/>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>AM015</t>
+        </is>
+      </c>
+      <c r="B17" s="16" t="n"/>
+      <c r="D17" s="15" t="inlineStr">
         <is>
           <t>AM005</t>
         </is>
       </c>
-      <c r="B15" s="17" t="n"/>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>AM005</t>
-        </is>
-      </c>
-      <c r="E15" s="17" t="n"/>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="16" t="inlineStr">
+      <c r="E17" s="16" t="n"/>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>AM022</t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="n"/>
+      <c r="D18" s="15" t="inlineStr">
         <is>
           <t>AM014</t>
         </is>
       </c>
-      <c r="B16" s="17" t="n"/>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>AM014</t>
-        </is>
-      </c>
-      <c r="E16" s="17" t="n"/>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="16" t="inlineStr">
+      <c r="E18" s="16" t="n"/>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>AM024</t>
+        </is>
+      </c>
+      <c r="B19" s="16" t="n"/>
+      <c r="D19" s="15" t="inlineStr">
         <is>
           <t>AM015</t>
         </is>
       </c>
-      <c r="B17" s="17" t="n"/>
-      <c r="D17" s="16" t="inlineStr">
-        <is>
-          <t>AM015</t>
-        </is>
-      </c>
-      <c r="E17" s="17" t="n"/>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="16" t="inlineStr">
+      <c r="E19" s="16" t="n"/>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>AM026</t>
+        </is>
+      </c>
+      <c r="B20" s="16" t="n"/>
+      <c r="D20" s="15" t="inlineStr">
         <is>
           <t>AM022</t>
         </is>
       </c>
-      <c r="B18" s="17" t="n"/>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>AM022</t>
-        </is>
-      </c>
-      <c r="E18" s="17" t="n"/>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="E20" s="16" t="n"/>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="D21" s="15" t="inlineStr">
         <is>
           <t>AM024</t>
         </is>
       </c>
-      <c r="B19" s="17" t="n"/>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>AM024</t>
-        </is>
-      </c>
-      <c r="E19" s="17" t="n"/>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="16" t="inlineStr">
+      <c r="E21" s="16" t="n"/>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="D22" s="15" t="inlineStr">
         <is>
           <t>AM026</t>
         </is>
       </c>
-      <c r="B20" s="17" t="n"/>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>AM026</t>
-        </is>
-      </c>
-      <c r="E20" s="17" t="n"/>
-    </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>ℹ  After pasting your own data the lists above update automatically. If the dropdown (B3 / E3) doesn't show your names, right-click the cell → Data Validation → update the Source range to match your column headers. Values of -999 are treated as no-data and excluded from calculations.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="18" t="inlineStr">
+      <c r="E22" s="16" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>ℹ  Use Pressure 1 / 2 / 3 dropdowns (E3:E5) to overlay up to 3 pressure series on the chart.  Leave E4 or E5 blank to show fewer series.  Leave B3 blank to hide the flow line and show pressure only.  After pasting your own data, right-click each selector cell → Data Validation → update the Source to match your column headers.  Values of -999 are treated as no-data and excluded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="18" t="inlineStr">
         <is>
           <t>FORMULA TABLE  —  updates automatically when you change the selections or adjustments above</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="1" t="inlineStr">
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Flow (Raw)</t>
         </is>
       </c>
-      <c r="C24" s="19" t="inlineStr">
+      <c r="C26" s="19" t="inlineStr">
         <is>
           <t>Flow Adjusted</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>Pressure (Raw)</t>
-        </is>
-      </c>
-      <c r="E24" s="20" t="inlineStr">
-        <is>
-          <t>Pressure Adjusted</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="21">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
-        <v/>
-      </c>
-      <c r="B25" s="22">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C25" s="23">
-        <f>IF(OR(B25="",B25=-999),"",B25*$B$2)</f>
-        <v/>
-      </c>
-      <c r="D25" s="22">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="E25" s="24">
-        <f>IF(OR(D25="",D25=-999),"",D25+$E$2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
-        <v/>
-      </c>
-      <c r="B26" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C26" s="27">
-        <f>IF(OR(B26="",B26=-999),"",B26*$B$2)</f>
-        <v/>
-      </c>
-      <c r="D26" s="26">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="E26" s="28">
-        <f>IF(OR(D26="",D26=-999),"",D26+$E$2)</f>
-        <v/>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Pressure 1 (Raw)</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>Pressure 1 Adj.</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Pressure 2 (Raw)</t>
+        </is>
+      </c>
+      <c r="G26" s="20" t="inlineStr">
+        <is>
+          <t>Pressure 2 Adj.</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Pressure 3 (Raw)</t>
+        </is>
+      </c>
+      <c r="I26" s="20" t="inlineStr">
+        <is>
+          <t>Pressure 3 Adj.</t>
+        </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="21">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B27" s="22">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C27" s="23">
@@ -4617,21 +5208,37 @@
         <v/>
       </c>
       <c r="D27" s="22">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E27" s="24">
         <f>IF(OR(D27="",D27=-999),"",D27+$E$2)</f>
         <v/>
       </c>
+      <c r="F27" s="22">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G27" s="24">
+        <f>IF(OR(F27="",F27=-999),"",F27+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H27" s="22">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I27" s="24">
+        <f>IF(OR(H27="",H27=-999),"",H27+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B28" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C28" s="27">
@@ -4639,21 +5246,37 @@
         <v/>
       </c>
       <c r="D28" s="26">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E28" s="28">
         <f>IF(OR(D28="",D28=-999),"",D28+$E$2)</f>
         <v/>
       </c>
+      <c r="F28" s="26">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G28" s="28">
+        <f>IF(OR(F28="",F28=-999),"",F28+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H28" s="26">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I28" s="28">
+        <f>IF(OR(H28="",H28=-999),"",H28+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" s="21">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B29" s="22">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C29" s="23">
@@ -4661,21 +5284,37 @@
         <v/>
       </c>
       <c r="D29" s="22">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E29" s="24">
         <f>IF(OR(D29="",D29=-999),"",D29+$E$2)</f>
         <v/>
       </c>
+      <c r="F29" s="22">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G29" s="24">
+        <f>IF(OR(F29="",F29=-999),"",F29+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H29" s="22">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I29" s="24">
+        <f>IF(OR(H29="",H29=-999),"",H29+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B30" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C30" s="27">
@@ -4683,21 +5322,37 @@
         <v/>
       </c>
       <c r="D30" s="26">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E30" s="28">
         <f>IF(OR(D30="",D30=-999),"",D30+$E$2)</f>
         <v/>
       </c>
+      <c r="F30" s="26">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G30" s="28">
+        <f>IF(OR(F30="",F30=-999),"",F30+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H30" s="26">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I30" s="28">
+        <f>IF(OR(H30="",H30=-999),"",H30+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" s="21">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B31" s="22">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C31" s="23">
@@ -4705,21 +5360,37 @@
         <v/>
       </c>
       <c r="D31" s="22">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E31" s="24">
         <f>IF(OR(D31="",D31=-999),"",D31+$E$2)</f>
         <v/>
       </c>
+      <c r="F31" s="22">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G31" s="24">
+        <f>IF(OR(F31="",F31=-999),"",F31+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H31" s="22">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I31" s="24">
+        <f>IF(OR(H31="",H31=-999),"",H31+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B32" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C32" s="27">
@@ -4727,21 +5398,37 @@
         <v/>
       </c>
       <c r="D32" s="26">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E32" s="28">
         <f>IF(OR(D32="",D32=-999),"",D32+$E$2)</f>
         <v/>
       </c>
+      <c r="F32" s="26">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G32" s="28">
+        <f>IF(OR(F32="",F32=-999),"",F32+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H32" s="26">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I32" s="28">
+        <f>IF(OR(H32="",H32=-999),"",H32+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" s="21">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B33" s="22">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C33" s="23">
@@ -4749,21 +5436,37 @@
         <v/>
       </c>
       <c r="D33" s="22">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E33" s="24">
         <f>IF(OR(D33="",D33=-999),"",D33+$E$2)</f>
         <v/>
       </c>
+      <c r="F33" s="22">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G33" s="24">
+        <f>IF(OR(F33="",F33=-999),"",F33+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H33" s="22">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I33" s="24">
+        <f>IF(OR(H33="",H33=-999),"",H33+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B34" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C34" s="27">
@@ -4771,21 +5474,37 @@
         <v/>
       </c>
       <c r="D34" s="26">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E34" s="28">
         <f>IF(OR(D34="",D34=-999),"",D34+$E$2)</f>
         <v/>
       </c>
+      <c r="F34" s="26">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G34" s="28">
+        <f>IF(OR(F34="",F34=-999),"",F34+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H34" s="26">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I34" s="28">
+        <f>IF(OR(H34="",H34=-999),"",H34+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" s="21">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B35" s="22">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C35" s="23">
@@ -4793,21 +5512,37 @@
         <v/>
       </c>
       <c r="D35" s="22">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E35" s="24">
         <f>IF(OR(D35="",D35=-999),"",D35+$E$2)</f>
         <v/>
       </c>
+      <c r="F35" s="22">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G35" s="24">
+        <f>IF(OR(F35="",F35=-999),"",F35+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H35" s="22">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I35" s="24">
+        <f>IF(OR(H35="",H35=-999),"",H35+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B36" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C36" s="27">
@@ -4815,21 +5550,37 @@
         <v/>
       </c>
       <c r="D36" s="26">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E36" s="28">
         <f>IF(OR(D36="",D36=-999),"",D36+$E$2)</f>
         <v/>
       </c>
+      <c r="F36" s="26">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G36" s="28">
+        <f>IF(OR(F36="",F36=-999),"",F36+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H36" s="26">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I36" s="28">
+        <f>IF(OR(H36="",H36=-999),"",H36+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" s="21">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B37" s="22">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C37" s="23">
@@ -4837,21 +5588,37 @@
         <v/>
       </c>
       <c r="D37" s="22">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E37" s="24">
         <f>IF(OR(D37="",D37=-999),"",D37+$E$2)</f>
         <v/>
       </c>
+      <c r="F37" s="22">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G37" s="24">
+        <f>IF(OR(F37="",F37=-999),"",F37+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H37" s="22">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I37" s="24">
+        <f>IF(OR(H37="",H37=-999),"",H37+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B38" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C38" s="27">
@@ -4859,21 +5626,37 @@
         <v/>
       </c>
       <c r="D38" s="26">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E38" s="28">
         <f>IF(OR(D38="",D38=-999),"",D38+$E$2)</f>
         <v/>
       </c>
+      <c r="F38" s="26">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G38" s="28">
+        <f>IF(OR(F38="",F38=-999),"",F38+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H38" s="26">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I38" s="28">
+        <f>IF(OR(H38="",H38=-999),"",H38+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" s="21">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B39" s="22">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C39" s="23">
@@ -4881,21 +5664,37 @@
         <v/>
       </c>
       <c r="D39" s="22">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E39" s="24">
         <f>IF(OR(D39="",D39=-999),"",D39+$E$2)</f>
         <v/>
       </c>
+      <c r="F39" s="22">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G39" s="24">
+        <f>IF(OR(F39="",F39=-999),"",F39+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H39" s="22">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I39" s="24">
+        <f>IF(OR(H39="",H39=-999),"",H39+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B40" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C40" s="27">
@@ -4903,21 +5702,37 @@
         <v/>
       </c>
       <c r="D40" s="26">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E40" s="28">
         <f>IF(OR(D40="",D40=-999),"",D40+$E$2)</f>
         <v/>
       </c>
+      <c r="F40" s="26">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G40" s="28">
+        <f>IF(OR(F40="",F40=-999),"",F40+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H40" s="26">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I40" s="28">
+        <f>IF(OR(H40="",H40=-999),"",H40+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" s="21">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B41" s="22">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C41" s="23">
@@ -4925,21 +5740,37 @@
         <v/>
       </c>
       <c r="D41" s="22">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E41" s="24">
         <f>IF(OR(D41="",D41=-999),"",D41+$E$2)</f>
         <v/>
       </c>
+      <c r="F41" s="22">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G41" s="24">
+        <f>IF(OR(F41="",F41=-999),"",F41+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H41" s="22">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I41" s="24">
+        <f>IF(OR(H41="",H41=-999),"",H41+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B42" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C42" s="27">
@@ -4947,21 +5778,37 @@
         <v/>
       </c>
       <c r="D42" s="26">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E42" s="28">
         <f>IF(OR(D42="",D42=-999),"",D42+$E$2)</f>
         <v/>
       </c>
+      <c r="F42" s="26">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G42" s="28">
+        <f>IF(OR(F42="",F42=-999),"",F42+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H42" s="26">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I42" s="28">
+        <f>IF(OR(H42="",H42=-999),"",H42+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" s="21">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B43" s="22">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C43" s="23">
@@ -4969,21 +5816,37 @@
         <v/>
       </c>
       <c r="D43" s="22">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E43" s="24">
         <f>IF(OR(D43="",D43=-999),"",D43+$E$2)</f>
         <v/>
       </c>
+      <c r="F43" s="22">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G43" s="24">
+        <f>IF(OR(F43="",F43=-999),"",F43+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H43" s="22">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I43" s="24">
+        <f>IF(OR(H43="",H43=-999),"",H43+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B44" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C44" s="27">
@@ -4991,21 +5854,37 @@
         <v/>
       </c>
       <c r="D44" s="26">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E44" s="28">
         <f>IF(OR(D44="",D44=-999),"",D44+$E$2)</f>
         <v/>
       </c>
+      <c r="F44" s="26">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G44" s="28">
+        <f>IF(OR(F44="",F44=-999),"",F44+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H44" s="26">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I44" s="28">
+        <f>IF(OR(H44="",H44=-999),"",H44+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" s="21">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B45" s="22">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C45" s="23">
@@ -5013,21 +5892,37 @@
         <v/>
       </c>
       <c r="D45" s="22">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E45" s="24">
         <f>IF(OR(D45="",D45=-999),"",D45+$E$2)</f>
         <v/>
       </c>
+      <c r="F45" s="22">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G45" s="24">
+        <f>IF(OR(F45="",F45=-999),"",F45+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H45" s="22">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I45" s="24">
+        <f>IF(OR(H45="",H45=-999),"",H45+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B46" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C46" s="27">
@@ -5035,21 +5930,37 @@
         <v/>
       </c>
       <c r="D46" s="26">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E46" s="28">
         <f>IF(OR(D46="",D46=-999),"",D46+$E$2)</f>
         <v/>
       </c>
+      <c r="F46" s="26">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G46" s="28">
+        <f>IF(OR(F46="",F46=-999),"",F46+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H46" s="26">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I46" s="28">
+        <f>IF(OR(H46="",H46=-999),"",H46+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" s="21">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B47" s="22">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C47" s="23">
@@ -5057,21 +5968,37 @@
         <v/>
       </c>
       <c r="D47" s="22">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E47" s="24">
         <f>IF(OR(D47="",D47=-999),"",D47+$E$2)</f>
         <v/>
       </c>
+      <c r="F47" s="22">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G47" s="24">
+        <f>IF(OR(F47="",F47=-999),"",F47+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H47" s="22">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I47" s="24">
+        <f>IF(OR(H47="",H47=-999),"",H47+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B48" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C48" s="27">
@@ -5079,21 +6006,37 @@
         <v/>
       </c>
       <c r="D48" s="26">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E48" s="28">
         <f>IF(OR(D48="",D48=-999),"",D48+$E$2)</f>
         <v/>
       </c>
+      <c r="F48" s="26">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G48" s="28">
+        <f>IF(OR(F48="",F48=-999),"",F48+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H48" s="26">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I48" s="28">
+        <f>IF(OR(H48="",H48=-999),"",H48+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" s="21">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B49" s="22">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C49" s="23">
@@ -5101,21 +6044,37 @@
         <v/>
       </c>
       <c r="D49" s="22">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E49" s="24">
         <f>IF(OR(D49="",D49=-999),"",D49+$E$2)</f>
         <v/>
       </c>
+      <c r="F49" s="22">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G49" s="24">
+        <f>IF(OR(F49="",F49=-999),"",F49+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H49" s="22">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I49" s="24">
+        <f>IF(OR(H49="",H49=-999),"",H49+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B50" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C50" s="27">
@@ -5123,21 +6082,37 @@
         <v/>
       </c>
       <c r="D50" s="26">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E50" s="28">
         <f>IF(OR(D50="",D50=-999),"",D50+$E$2)</f>
         <v/>
       </c>
+      <c r="F50" s="26">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G50" s="28">
+        <f>IF(OR(F50="",F50=-999),"",F50+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H50" s="26">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I50" s="28">
+        <f>IF(OR(H50="",H50=-999),"",H50+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" s="21">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B51" s="22">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C51" s="23">
@@ -5145,21 +6120,37 @@
         <v/>
       </c>
       <c r="D51" s="22">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E51" s="24">
         <f>IF(OR(D51="",D51=-999),"",D51+$E$2)</f>
         <v/>
       </c>
+      <c r="F51" s="22">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G51" s="24">
+        <f>IF(OR(F51="",F51=-999),"",F51+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H51" s="22">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I51" s="24">
+        <f>IF(OR(H51="",H51=-999),"",H51+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="52" ht="15" customHeight="1">
       <c r="A52" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B52" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C52" s="27">
@@ -5167,21 +6158,37 @@
         <v/>
       </c>
       <c r="D52" s="26">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E52" s="28">
         <f>IF(OR(D52="",D52=-999),"",D52+$E$2)</f>
         <v/>
       </c>
+      <c r="F52" s="26">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G52" s="28">
+        <f>IF(OR(F52="",F52=-999),"",F52+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H52" s="26">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I52" s="28">
+        <f>IF(OR(H52="",H52=-999),"",H52+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="53" ht="15" customHeight="1">
       <c r="A53" s="21">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B53" s="22">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C53" s="23">
@@ -5189,21 +6196,37 @@
         <v/>
       </c>
       <c r="D53" s="22">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E53" s="24">
         <f>IF(OR(D53="",D53=-999),"",D53+$E$2)</f>
         <v/>
       </c>
+      <c r="F53" s="22">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G53" s="24">
+        <f>IF(OR(F53="",F53=-999),"",F53+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H53" s="22">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I53" s="24">
+        <f>IF(OR(H53="",H53=-999),"",H53+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="54" ht="15" customHeight="1">
       <c r="A54" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B54" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C54" s="27">
@@ -5211,21 +6234,37 @@
         <v/>
       </c>
       <c r="D54" s="26">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E54" s="28">
         <f>IF(OR(D54="",D54=-999),"",D54+$E$2)</f>
         <v/>
       </c>
+      <c r="F54" s="26">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G54" s="28">
+        <f>IF(OR(F54="",F54=-999),"",F54+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H54" s="26">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I54" s="28">
+        <f>IF(OR(H54="",H54=-999),"",H54+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="55" ht="15" customHeight="1">
       <c r="A55" s="21">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B55" s="22">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C55" s="23">
@@ -5233,21 +6272,37 @@
         <v/>
       </c>
       <c r="D55" s="22">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E55" s="24">
         <f>IF(OR(D55="",D55=-999),"",D55+$E$2)</f>
         <v/>
       </c>
+      <c r="F55" s="22">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G55" s="24">
+        <f>IF(OR(F55="",F55=-999),"",F55+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H55" s="22">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I55" s="24">
+        <f>IF(OR(H55="",H55=-999),"",H55+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="56" ht="15" customHeight="1">
       <c r="A56" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B56" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C56" s="27">
@@ -5255,21 +6310,37 @@
         <v/>
       </c>
       <c r="D56" s="26">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E56" s="28">
         <f>IF(OR(D56="",D56=-999),"",D56+$E$2)</f>
         <v/>
       </c>
+      <c r="F56" s="26">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G56" s="28">
+        <f>IF(OR(F56="",F56=-999),"",F56+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H56" s="26">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I56" s="28">
+        <f>IF(OR(H56="",H56=-999),"",H56+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="57" ht="15" customHeight="1">
       <c r="A57" s="21">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B57" s="22">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C57" s="23">
@@ -5277,21 +6348,37 @@
         <v/>
       </c>
       <c r="D57" s="22">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E57" s="24">
         <f>IF(OR(D57="",D57=-999),"",D57+$E$2)</f>
         <v/>
       </c>
+      <c r="F57" s="22">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G57" s="24">
+        <f>IF(OR(F57="",F57=-999),"",F57+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H57" s="22">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I57" s="24">
+        <f>IF(OR(H57="",H57=-999),"",H57+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="58" ht="15" customHeight="1">
       <c r="A58" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B58" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C58" s="27">
@@ -5299,21 +6386,37 @@
         <v/>
       </c>
       <c r="D58" s="26">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E58" s="28">
         <f>IF(OR(D58="",D58=-999),"",D58+$E$2)</f>
         <v/>
       </c>
+      <c r="F58" s="26">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G58" s="28">
+        <f>IF(OR(F58="",F58=-999),"",F58+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H58" s="26">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I58" s="28">
+        <f>IF(OR(H58="",H58=-999),"",H58+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="59" ht="15" customHeight="1">
       <c r="A59" s="21">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B59" s="22">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C59" s="23">
@@ -5321,21 +6424,37 @@
         <v/>
       </c>
       <c r="D59" s="22">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E59" s="24">
         <f>IF(OR(D59="",D59=-999),"",D59+$E$2)</f>
         <v/>
       </c>
+      <c r="F59" s="22">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G59" s="24">
+        <f>IF(OR(F59="",F59=-999),"",F59+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H59" s="22">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I59" s="24">
+        <f>IF(OR(H59="",H59=-999),"",H59+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="60" ht="15" customHeight="1">
       <c r="A60" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B60" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C60" s="27">
@@ -5343,21 +6462,37 @@
         <v/>
       </c>
       <c r="D60" s="26">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E60" s="28">
         <f>IF(OR(D60="",D60=-999),"",D60+$E$2)</f>
         <v/>
       </c>
+      <c r="F60" s="26">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G60" s="28">
+        <f>IF(OR(F60="",F60=-999),"",F60+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H60" s="26">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I60" s="28">
+        <f>IF(OR(H60="",H60=-999),"",H60+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="61" ht="15" customHeight="1">
       <c r="A61" s="21">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B61" s="22">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C61" s="23">
@@ -5365,21 +6500,37 @@
         <v/>
       </c>
       <c r="D61" s="22">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E61" s="24">
         <f>IF(OR(D61="",D61=-999),"",D61+$E$2)</f>
         <v/>
       </c>
+      <c r="F61" s="22">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G61" s="24">
+        <f>IF(OR(F61="",F61=-999),"",F61+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H61" s="22">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I61" s="24">
+        <f>IF(OR(H61="",H61=-999),"",H61+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="62" ht="15" customHeight="1">
       <c r="A62" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B62" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C62" s="27">
@@ -5387,21 +6538,37 @@
         <v/>
       </c>
       <c r="D62" s="26">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E62" s="28">
         <f>IF(OR(D62="",D62=-999),"",D62+$E$2)</f>
         <v/>
       </c>
+      <c r="F62" s="26">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G62" s="28">
+        <f>IF(OR(F62="",F62=-999),"",F62+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H62" s="26">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I62" s="28">
+        <f>IF(OR(H62="",H62=-999),"",H62+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="63" ht="15" customHeight="1">
       <c r="A63" s="21">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B63" s="22">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C63" s="23">
@@ -5409,21 +6576,37 @@
         <v/>
       </c>
       <c r="D63" s="22">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E63" s="24">
         <f>IF(OR(D63="",D63=-999),"",D63+$E$2)</f>
         <v/>
       </c>
+      <c r="F63" s="22">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G63" s="24">
+        <f>IF(OR(F63="",F63=-999),"",F63+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H63" s="22">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I63" s="24">
+        <f>IF(OR(H63="",H63=-999),"",H63+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="64" ht="15" customHeight="1">
       <c r="A64" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B64" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C64" s="27">
@@ -5431,21 +6614,37 @@
         <v/>
       </c>
       <c r="D64" s="26">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E64" s="28">
         <f>IF(OR(D64="",D64=-999),"",D64+$E$2)</f>
         <v/>
       </c>
+      <c r="F64" s="26">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G64" s="28">
+        <f>IF(OR(F64="",F64=-999),"",F64+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H64" s="26">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I64" s="28">
+        <f>IF(OR(H64="",H64=-999),"",H64+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="65" ht="15" customHeight="1">
       <c r="A65" s="21">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B65" s="22">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C65" s="23">
@@ -5453,21 +6652,37 @@
         <v/>
       </c>
       <c r="D65" s="22">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E65" s="24">
         <f>IF(OR(D65="",D65=-999),"",D65+$E$2)</f>
         <v/>
       </c>
+      <c r="F65" s="22">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G65" s="24">
+        <f>IF(OR(F65="",F65=-999),"",F65+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H65" s="22">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I65" s="24">
+        <f>IF(OR(H65="",H65=-999),"",H65+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="66" ht="15" customHeight="1">
       <c r="A66" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B66" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C66" s="27">
@@ -5475,21 +6690,37 @@
         <v/>
       </c>
       <c r="D66" s="26">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E66" s="28">
         <f>IF(OR(D66="",D66=-999),"",D66+$E$2)</f>
         <v/>
       </c>
+      <c r="F66" s="26">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G66" s="28">
+        <f>IF(OR(F66="",F66=-999),"",F66+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H66" s="26">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I66" s="28">
+        <f>IF(OR(H66="",H66=-999),"",H66+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="67" ht="15" customHeight="1">
       <c r="A67" s="21">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B67" s="22">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C67" s="23">
@@ -5497,21 +6728,37 @@
         <v/>
       </c>
       <c r="D67" s="22">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E67" s="24">
         <f>IF(OR(D67="",D67=-999),"",D67+$E$2)</f>
         <v/>
       </c>
+      <c r="F67" s="22">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G67" s="24">
+        <f>IF(OR(F67="",F67=-999),"",F67+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H67" s="22">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I67" s="24">
+        <f>IF(OR(H67="",H67=-999),"",H67+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="68" ht="15" customHeight="1">
       <c r="A68" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B68" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C68" s="27">
@@ -5519,21 +6766,37 @@
         <v/>
       </c>
       <c r="D68" s="26">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E68" s="28">
         <f>IF(OR(D68="",D68=-999),"",D68+$E$2)</f>
         <v/>
       </c>
+      <c r="F68" s="26">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G68" s="28">
+        <f>IF(OR(F68="",F68=-999),"",F68+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H68" s="26">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I68" s="28">
+        <f>IF(OR(H68="",H68=-999),"",H68+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="69" ht="15" customHeight="1">
       <c r="A69" s="21">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B69" s="22">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C69" s="23">
@@ -5541,21 +6804,37 @@
         <v/>
       </c>
       <c r="D69" s="22">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E69" s="24">
         <f>IF(OR(D69="",D69=-999),"",D69+$E$2)</f>
         <v/>
       </c>
+      <c r="F69" s="22">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G69" s="24">
+        <f>IF(OR(F69="",F69=-999),"",F69+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H69" s="22">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I69" s="24">
+        <f>IF(OR(H69="",H69=-999),"",H69+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="70" ht="15" customHeight="1">
       <c r="A70" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B70" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C70" s="27">
@@ -5563,21 +6842,37 @@
         <v/>
       </c>
       <c r="D70" s="26">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E70" s="28">
         <f>IF(OR(D70="",D70=-999),"",D70+$E$2)</f>
         <v/>
       </c>
+      <c r="F70" s="26">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G70" s="28">
+        <f>IF(OR(F70="",F70=-999),"",F70+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H70" s="26">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I70" s="28">
+        <f>IF(OR(H70="",H70=-999),"",H70+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="71" ht="15" customHeight="1">
       <c r="A71" s="21">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B71" s="22">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C71" s="23">
@@ -5585,21 +6880,37 @@
         <v/>
       </c>
       <c r="D71" s="22">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E71" s="24">
         <f>IF(OR(D71="",D71=-999),"",D71+$E$2)</f>
         <v/>
       </c>
+      <c r="F71" s="22">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G71" s="24">
+        <f>IF(OR(F71="",F71=-999),"",F71+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H71" s="22">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I71" s="24">
+        <f>IF(OR(H71="",H71=-999),"",H71+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="72" ht="15" customHeight="1">
       <c r="A72" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B72" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C72" s="27">
@@ -5607,21 +6918,37 @@
         <v/>
       </c>
       <c r="D72" s="26">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E72" s="28">
         <f>IF(OR(D72="",D72=-999),"",D72+$E$2)</f>
         <v/>
       </c>
+      <c r="F72" s="26">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G72" s="28">
+        <f>IF(OR(F72="",F72=-999),"",F72+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H72" s="26">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I72" s="28">
+        <f>IF(OR(H72="",H72=-999),"",H72+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="73" ht="15" customHeight="1">
       <c r="A73" s="21">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B73" s="22">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C73" s="23">
@@ -5629,21 +6956,37 @@
         <v/>
       </c>
       <c r="D73" s="22">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E73" s="24">
         <f>IF(OR(D73="",D73=-999),"",D73+$E$2)</f>
         <v/>
       </c>
+      <c r="F73" s="22">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G73" s="24">
+        <f>IF(OR(F73="",F73=-999),"",F73+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H73" s="22">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I73" s="24">
+        <f>IF(OR(H73="",H73=-999),"",H73+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="74" ht="15" customHeight="1">
       <c r="A74" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B74" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C74" s="27">
@@ -5651,21 +6994,37 @@
         <v/>
       </c>
       <c r="D74" s="26">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E74" s="28">
         <f>IF(OR(D74="",D74=-999),"",D74+$E$2)</f>
         <v/>
       </c>
+      <c r="F74" s="26">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G74" s="28">
+        <f>IF(OR(F74="",F74=-999),"",F74+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H74" s="26">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I74" s="28">
+        <f>IF(OR(H74="",H74=-999),"",H74+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="75" ht="15" customHeight="1">
       <c r="A75" s="21">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B75" s="22">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C75" s="23">
@@ -5673,21 +7032,37 @@
         <v/>
       </c>
       <c r="D75" s="22">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E75" s="24">
         <f>IF(OR(D75="",D75=-999),"",D75+$E$2)</f>
         <v/>
       </c>
+      <c r="F75" s="22">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G75" s="24">
+        <f>IF(OR(F75="",F75=-999),"",F75+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H75" s="22">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I75" s="24">
+        <f>IF(OR(H75="",H75=-999),"",H75+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="76" ht="15" customHeight="1">
       <c r="A76" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B76" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C76" s="27">
@@ -5695,21 +7070,37 @@
         <v/>
       </c>
       <c r="D76" s="26">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E76" s="28">
         <f>IF(OR(D76="",D76=-999),"",D76+$E$2)</f>
         <v/>
       </c>
+      <c r="F76" s="26">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G76" s="28">
+        <f>IF(OR(F76="",F76=-999),"",F76+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H76" s="26">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I76" s="28">
+        <f>IF(OR(H76="",H76=-999),"",H76+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="77" ht="15" customHeight="1">
       <c r="A77" s="21">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B77" s="22">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C77" s="23">
@@ -5717,21 +7108,37 @@
         <v/>
       </c>
       <c r="D77" s="22">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E77" s="24">
         <f>IF(OR(D77="",D77=-999),"",D77+$E$2)</f>
         <v/>
       </c>
+      <c r="F77" s="22">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G77" s="24">
+        <f>IF(OR(F77="",F77=-999),"",F77+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H77" s="22">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I77" s="24">
+        <f>IF(OR(H77="",H77=-999),"",H77+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="78" ht="15" customHeight="1">
       <c r="A78" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B78" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C78" s="27">
@@ -5739,21 +7146,37 @@
         <v/>
       </c>
       <c r="D78" s="26">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E78" s="28">
         <f>IF(OR(D78="",D78=-999),"",D78+$E$2)</f>
         <v/>
       </c>
+      <c r="F78" s="26">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G78" s="28">
+        <f>IF(OR(F78="",F78=-999),"",F78+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H78" s="26">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I78" s="28">
+        <f>IF(OR(H78="",H78=-999),"",H78+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="79" ht="15" customHeight="1">
       <c r="A79" s="21">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B79" s="22">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C79" s="23">
@@ -5761,21 +7184,37 @@
         <v/>
       </c>
       <c r="D79" s="22">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E79" s="24">
         <f>IF(OR(D79="",D79=-999),"",D79+$E$2)</f>
         <v/>
       </c>
+      <c r="F79" s="22">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G79" s="24">
+        <f>IF(OR(F79="",F79=-999),"",F79+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H79" s="22">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I79" s="24">
+        <f>IF(OR(H79="",H79=-999),"",H79+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="80" ht="15" customHeight="1">
       <c r="A80" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B80" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C80" s="27">
@@ -5783,21 +7222,37 @@
         <v/>
       </c>
       <c r="D80" s="26">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E80" s="28">
         <f>IF(OR(D80="",D80=-999),"",D80+$E$2)</f>
         <v/>
       </c>
+      <c r="F80" s="26">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G80" s="28">
+        <f>IF(OR(F80="",F80=-999),"",F80+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H80" s="26">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I80" s="28">
+        <f>IF(OR(H80="",H80=-999),"",H80+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="81" ht="15" customHeight="1">
       <c r="A81" s="21">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B81" s="22">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C81" s="23">
@@ -5805,21 +7260,37 @@
         <v/>
       </c>
       <c r="D81" s="22">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E81" s="24">
         <f>IF(OR(D81="",D81=-999),"",D81+$E$2)</f>
         <v/>
       </c>
+      <c r="F81" s="22">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G81" s="24">
+        <f>IF(OR(F81="",F81=-999),"",F81+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H81" s="22">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I81" s="24">
+        <f>IF(OR(H81="",H81=-999),"",H81+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="82" ht="15" customHeight="1">
       <c r="A82" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B82" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C82" s="27">
@@ -5827,21 +7298,37 @@
         <v/>
       </c>
       <c r="D82" s="26">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E82" s="28">
         <f>IF(OR(D82="",D82=-999),"",D82+$E$2)</f>
         <v/>
       </c>
+      <c r="F82" s="26">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G82" s="28">
+        <f>IF(OR(F82="",F82=-999),"",F82+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H82" s="26">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I82" s="28">
+        <f>IF(OR(H82="",H82=-999),"",H82+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="83" ht="15" customHeight="1">
       <c r="A83" s="21">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B83" s="22">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C83" s="23">
@@ -5849,21 +7336,37 @@
         <v/>
       </c>
       <c r="D83" s="22">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E83" s="24">
         <f>IF(OR(D83="",D83=-999),"",D83+$E$2)</f>
         <v/>
       </c>
+      <c r="F83" s="22">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G83" s="24">
+        <f>IF(OR(F83="",F83=-999),"",F83+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H83" s="22">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I83" s="24">
+        <f>IF(OR(H83="",H83=-999),"",H83+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="84" ht="15" customHeight="1">
       <c r="A84" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B84" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C84" s="27">
@@ -5871,21 +7374,37 @@
         <v/>
       </c>
       <c r="D84" s="26">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E84" s="28">
         <f>IF(OR(D84="",D84=-999),"",D84+$E$2)</f>
         <v/>
       </c>
+      <c r="F84" s="26">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G84" s="28">
+        <f>IF(OR(F84="",F84=-999),"",F84+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H84" s="26">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I84" s="28">
+        <f>IF(OR(H84="",H84=-999),"",H84+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="85" ht="15" customHeight="1">
       <c r="A85" s="21">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B85" s="22">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C85" s="23">
@@ -5893,21 +7412,37 @@
         <v/>
       </c>
       <c r="D85" s="22">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E85" s="24">
         <f>IF(OR(D85="",D85=-999),"",D85+$E$2)</f>
         <v/>
       </c>
+      <c r="F85" s="22">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G85" s="24">
+        <f>IF(OR(F85="",F85=-999),"",F85+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H85" s="22">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I85" s="24">
+        <f>IF(OR(H85="",H85=-999),"",H85+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="86" ht="15" customHeight="1">
       <c r="A86" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B86" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C86" s="27">
@@ -5915,21 +7450,37 @@
         <v/>
       </c>
       <c r="D86" s="26">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E86" s="28">
         <f>IF(OR(D86="",D86=-999),"",D86+$E$2)</f>
         <v/>
       </c>
+      <c r="F86" s="26">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G86" s="28">
+        <f>IF(OR(F86="",F86=-999),"",F86+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H86" s="26">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I86" s="28">
+        <f>IF(OR(H86="",H86=-999),"",H86+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="87" ht="15" customHeight="1">
       <c r="A87" s="21">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B87" s="22">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C87" s="23">
@@ -5937,21 +7488,37 @@
         <v/>
       </c>
       <c r="D87" s="22">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E87" s="24">
         <f>IF(OR(D87="",D87=-999),"",D87+$E$2)</f>
         <v/>
       </c>
+      <c r="F87" s="22">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G87" s="24">
+        <f>IF(OR(F87="",F87=-999),"",F87+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H87" s="22">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I87" s="24">
+        <f>IF(OR(H87="",H87=-999),"",H87+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="88" ht="15" customHeight="1">
       <c r="A88" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B88" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C88" s="27">
@@ -5959,21 +7526,37 @@
         <v/>
       </c>
       <c r="D88" s="26">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E88" s="28">
         <f>IF(OR(D88="",D88=-999),"",D88+$E$2)</f>
         <v/>
       </c>
+      <c r="F88" s="26">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G88" s="28">
+        <f>IF(OR(F88="",F88=-999),"",F88+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H88" s="26">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I88" s="28">
+        <f>IF(OR(H88="",H88=-999),"",H88+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="89" ht="15" customHeight="1">
       <c r="A89" s="21">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B89" s="22">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C89" s="23">
@@ -5981,21 +7564,37 @@
         <v/>
       </c>
       <c r="D89" s="22">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E89" s="24">
         <f>IF(OR(D89="",D89=-999),"",D89+$E$2)</f>
         <v/>
       </c>
+      <c r="F89" s="22">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G89" s="24">
+        <f>IF(OR(F89="",F89=-999),"",F89+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H89" s="22">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I89" s="24">
+        <f>IF(OR(H89="",H89=-999),"",H89+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="90" ht="15" customHeight="1">
       <c r="A90" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B90" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C90" s="27">
@@ -6003,21 +7602,37 @@
         <v/>
       </c>
       <c r="D90" s="26">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E90" s="28">
         <f>IF(OR(D90="",D90=-999),"",D90+$E$2)</f>
         <v/>
       </c>
+      <c r="F90" s="26">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G90" s="28">
+        <f>IF(OR(F90="",F90=-999),"",F90+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H90" s="26">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I90" s="28">
+        <f>IF(OR(H90="",H90=-999),"",H90+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="91" ht="15" customHeight="1">
       <c r="A91" s="21">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B91" s="22">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C91" s="23">
@@ -6025,21 +7640,37 @@
         <v/>
       </c>
       <c r="D91" s="22">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E91" s="24">
         <f>IF(OR(D91="",D91=-999),"",D91+$E$2)</f>
         <v/>
       </c>
+      <c r="F91" s="22">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G91" s="24">
+        <f>IF(OR(F91="",F91=-999),"",F91+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H91" s="22">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I91" s="24">
+        <f>IF(OR(H91="",H91=-999),"",H91+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="92" ht="15" customHeight="1">
       <c r="A92" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B92" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C92" s="27">
@@ -6047,21 +7678,37 @@
         <v/>
       </c>
       <c r="D92" s="26">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E92" s="28">
         <f>IF(OR(D92="",D92=-999),"",D92+$E$2)</f>
         <v/>
       </c>
+      <c r="F92" s="26">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G92" s="28">
+        <f>IF(OR(F92="",F92=-999),"",F92+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H92" s="26">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I92" s="28">
+        <f>IF(OR(H92="",H92=-999),"",H92+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="93" ht="15" customHeight="1">
       <c r="A93" s="21">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B93" s="22">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C93" s="23">
@@ -6069,21 +7716,37 @@
         <v/>
       </c>
       <c r="D93" s="22">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E93" s="24">
         <f>IF(OR(D93="",D93=-999),"",D93+$E$2)</f>
         <v/>
       </c>
+      <c r="F93" s="22">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G93" s="24">
+        <f>IF(OR(F93="",F93=-999),"",F93+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H93" s="22">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I93" s="24">
+        <f>IF(OR(H93="",H93=-999),"",H93+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="94" ht="15" customHeight="1">
       <c r="A94" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B94" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C94" s="27">
@@ -6091,21 +7754,37 @@
         <v/>
       </c>
       <c r="D94" s="26">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E94" s="28">
         <f>IF(OR(D94="",D94=-999),"",D94+$E$2)</f>
         <v/>
       </c>
+      <c r="F94" s="26">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G94" s="28">
+        <f>IF(OR(F94="",F94=-999),"",F94+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H94" s="26">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I94" s="28">
+        <f>IF(OR(H94="",H94=-999),"",H94+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="95" ht="15" customHeight="1">
       <c r="A95" s="21">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B95" s="22">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C95" s="23">
@@ -6113,21 +7792,37 @@
         <v/>
       </c>
       <c r="D95" s="22">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E95" s="24">
         <f>IF(OR(D95="",D95=-999),"",D95+$E$2)</f>
         <v/>
       </c>
+      <c r="F95" s="22">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G95" s="24">
+        <f>IF(OR(F95="",F95=-999),"",F95+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H95" s="22">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I95" s="24">
+        <f>IF(OR(H95="",H95=-999),"",H95+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="96" ht="15" customHeight="1">
       <c r="A96" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B96" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C96" s="27">
@@ -6135,21 +7830,37 @@
         <v/>
       </c>
       <c r="D96" s="26">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E96" s="28">
         <f>IF(OR(D96="",D96=-999),"",D96+$E$2)</f>
         <v/>
       </c>
+      <c r="F96" s="26">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G96" s="28">
+        <f>IF(OR(F96="",F96=-999),"",F96+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H96" s="26">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I96" s="28">
+        <f>IF(OR(H96="",H96=-999),"",H96+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="97" ht="15" customHeight="1">
       <c r="A97" s="21">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B97" s="22">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C97" s="23">
@@ -6157,21 +7868,37 @@
         <v/>
       </c>
       <c r="D97" s="22">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E97" s="24">
         <f>IF(OR(D97="",D97=-999),"",D97+$E$2)</f>
         <v/>
       </c>
+      <c r="F97" s="22">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G97" s="24">
+        <f>IF(OR(F97="",F97=-999),"",F97+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H97" s="22">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I97" s="24">
+        <f>IF(OR(H97="",H97=-999),"",H97+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="98" ht="15" customHeight="1">
       <c r="A98" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B98" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C98" s="27">
@@ -6179,21 +7906,37 @@
         <v/>
       </c>
       <c r="D98" s="26">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E98" s="28">
         <f>IF(OR(D98="",D98=-999),"",D98+$E$2)</f>
         <v/>
       </c>
+      <c r="F98" s="26">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G98" s="28">
+        <f>IF(OR(F98="",F98=-999),"",F98+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H98" s="26">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I98" s="28">
+        <f>IF(OR(H98="",H98=-999),"",H98+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="99" ht="15" customHeight="1">
       <c r="A99" s="21">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B99" s="22">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C99" s="23">
@@ -6201,21 +7944,37 @@
         <v/>
       </c>
       <c r="D99" s="22">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E99" s="24">
         <f>IF(OR(D99="",D99=-999),"",D99+$E$2)</f>
         <v/>
       </c>
+      <c r="F99" s="22">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G99" s="24">
+        <f>IF(OR(F99="",F99=-999),"",F99+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H99" s="22">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I99" s="24">
+        <f>IF(OR(H99="",H99=-999),"",H99+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="100" ht="15" customHeight="1">
       <c r="A100" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B100" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C100" s="27">
@@ -6223,21 +7982,37 @@
         <v/>
       </c>
       <c r="D100" s="26">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E100" s="28">
         <f>IF(OR(D100="",D100=-999),"",D100+$E$2)</f>
         <v/>
       </c>
+      <c r="F100" s="26">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G100" s="28">
+        <f>IF(OR(F100="",F100=-999),"",F100+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H100" s="26">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I100" s="28">
+        <f>IF(OR(H100="",H100=-999),"",H100+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="101" ht="15" customHeight="1">
       <c r="A101" s="21">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B101" s="22">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C101" s="23">
@@ -6245,21 +8020,37 @@
         <v/>
       </c>
       <c r="D101" s="22">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E101" s="24">
         <f>IF(OR(D101="",D101=-999),"",D101+$E$2)</f>
         <v/>
       </c>
+      <c r="F101" s="22">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G101" s="24">
+        <f>IF(OR(F101="",F101=-999),"",F101+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H101" s="22">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I101" s="24">
+        <f>IF(OR(H101="",H101=-999),"",H101+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="102" ht="15" customHeight="1">
       <c r="A102" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B102" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C102" s="27">
@@ -6267,21 +8058,37 @@
         <v/>
       </c>
       <c r="D102" s="26">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E102" s="28">
         <f>IF(OR(D102="",D102=-999),"",D102+$E$2)</f>
         <v/>
       </c>
+      <c r="F102" s="26">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G102" s="28">
+        <f>IF(OR(F102="",F102=-999),"",F102+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H102" s="26">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I102" s="28">
+        <f>IF(OR(H102="",H102=-999),"",H102+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="103" ht="15" customHeight="1">
       <c r="A103" s="21">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B103" s="22">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C103" s="23">
@@ -6289,21 +8096,37 @@
         <v/>
       </c>
       <c r="D103" s="22">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E103" s="24">
         <f>IF(OR(D103="",D103=-999),"",D103+$E$2)</f>
         <v/>
       </c>
+      <c r="F103" s="22">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G103" s="24">
+        <f>IF(OR(F103="",F103=-999),"",F103+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H103" s="22">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I103" s="24">
+        <f>IF(OR(H103="",H103=-999),"",H103+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="104" ht="15" customHeight="1">
       <c r="A104" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B104" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C104" s="27">
@@ -6311,21 +8134,37 @@
         <v/>
       </c>
       <c r="D104" s="26">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E104" s="28">
         <f>IF(OR(D104="",D104=-999),"",D104+$E$2)</f>
         <v/>
       </c>
+      <c r="F104" s="26">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G104" s="28">
+        <f>IF(OR(F104="",F104=-999),"",F104+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H104" s="26">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I104" s="28">
+        <f>IF(OR(H104="",H104=-999),"",H104+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="105" ht="15" customHeight="1">
       <c r="A105" s="21">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B105" s="22">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C105" s="23">
@@ -6333,21 +8172,37 @@
         <v/>
       </c>
       <c r="D105" s="22">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E105" s="24">
         <f>IF(OR(D105="",D105=-999),"",D105+$E$2)</f>
         <v/>
       </c>
+      <c r="F105" s="22">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G105" s="24">
+        <f>IF(OR(F105="",F105=-999),"",F105+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H105" s="22">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I105" s="24">
+        <f>IF(OR(H105="",H105=-999),"",H105+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="106" ht="15" customHeight="1">
       <c r="A106" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B106" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C106" s="27">
@@ -6355,21 +8210,37 @@
         <v/>
       </c>
       <c r="D106" s="26">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E106" s="28">
         <f>IF(OR(D106="",D106=-999),"",D106+$E$2)</f>
         <v/>
       </c>
+      <c r="F106" s="26">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G106" s="28">
+        <f>IF(OR(F106="",F106=-999),"",F106+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H106" s="26">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I106" s="28">
+        <f>IF(OR(H106="",H106=-999),"",H106+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="107" ht="15" customHeight="1">
       <c r="A107" s="21">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B107" s="22">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C107" s="23">
@@ -6377,21 +8248,37 @@
         <v/>
       </c>
       <c r="D107" s="22">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E107" s="24">
         <f>IF(OR(D107="",D107=-999),"",D107+$E$2)</f>
         <v/>
       </c>
+      <c r="F107" s="22">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G107" s="24">
+        <f>IF(OR(F107="",F107=-999),"",F107+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H107" s="22">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I107" s="24">
+        <f>IF(OR(H107="",H107=-999),"",H107+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="108" ht="15" customHeight="1">
       <c r="A108" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B108" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C108" s="27">
@@ -6399,21 +8286,37 @@
         <v/>
       </c>
       <c r="D108" s="26">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E108" s="28">
         <f>IF(OR(D108="",D108=-999),"",D108+$E$2)</f>
         <v/>
       </c>
+      <c r="F108" s="26">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G108" s="28">
+        <f>IF(OR(F108="",F108=-999),"",F108+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H108" s="26">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I108" s="28">
+        <f>IF(OR(H108="",H108=-999),"",H108+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="109" ht="15" customHeight="1">
       <c r="A109" s="21">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B109" s="22">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C109" s="23">
@@ -6421,21 +8324,37 @@
         <v/>
       </c>
       <c r="D109" s="22">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E109" s="24">
         <f>IF(OR(D109="",D109=-999),"",D109+$E$2)</f>
         <v/>
       </c>
+      <c r="F109" s="22">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G109" s="24">
+        <f>IF(OR(F109="",F109=-999),"",F109+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H109" s="22">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I109" s="24">
+        <f>IF(OR(H109="",H109=-999),"",H109+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="110" ht="15" customHeight="1">
       <c r="A110" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B110" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C110" s="27">
@@ -6443,21 +8362,37 @@
         <v/>
       </c>
       <c r="D110" s="26">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E110" s="28">
         <f>IF(OR(D110="",D110=-999),"",D110+$E$2)</f>
         <v/>
       </c>
+      <c r="F110" s="26">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G110" s="28">
+        <f>IF(OR(F110="",F110=-999),"",F110+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H110" s="26">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I110" s="28">
+        <f>IF(OR(H110="",H110=-999),"",H110+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="111" ht="15" customHeight="1">
       <c r="A111" s="21">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B111" s="22">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C111" s="23">
@@ -6465,21 +8400,37 @@
         <v/>
       </c>
       <c r="D111" s="22">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E111" s="24">
         <f>IF(OR(D111="",D111=-999),"",D111+$E$2)</f>
         <v/>
       </c>
+      <c r="F111" s="22">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G111" s="24">
+        <f>IF(OR(F111="",F111=-999),"",F111+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H111" s="22">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I111" s="24">
+        <f>IF(OR(H111="",H111=-999),"",H111+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="112" ht="15" customHeight="1">
       <c r="A112" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B112" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C112" s="27">
@@ -6487,21 +8438,37 @@
         <v/>
       </c>
       <c r="D112" s="26">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E112" s="28">
         <f>IF(OR(D112="",D112=-999),"",D112+$E$2)</f>
         <v/>
       </c>
+      <c r="F112" s="26">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G112" s="28">
+        <f>IF(OR(F112="",F112=-999),"",F112+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H112" s="26">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I112" s="28">
+        <f>IF(OR(H112="",H112=-999),"",H112+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="113" ht="15" customHeight="1">
       <c r="A113" s="21">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B113" s="22">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C113" s="23">
@@ -6509,21 +8476,37 @@
         <v/>
       </c>
       <c r="D113" s="22">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E113" s="24">
         <f>IF(OR(D113="",D113=-999),"",D113+$E$2)</f>
         <v/>
       </c>
+      <c r="F113" s="22">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G113" s="24">
+        <f>IF(OR(F113="",F113=-999),"",F113+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H113" s="22">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I113" s="24">
+        <f>IF(OR(H113="",H113=-999),"",H113+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="114" ht="15" customHeight="1">
       <c r="A114" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B114" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C114" s="27">
@@ -6531,21 +8514,37 @@
         <v/>
       </c>
       <c r="D114" s="26">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E114" s="28">
         <f>IF(OR(D114="",D114=-999),"",D114+$E$2)</f>
         <v/>
       </c>
+      <c r="F114" s="26">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G114" s="28">
+        <f>IF(OR(F114="",F114=-999),"",F114+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H114" s="26">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I114" s="28">
+        <f>IF(OR(H114="",H114=-999),"",H114+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="115" ht="15" customHeight="1">
       <c r="A115" s="21">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B115" s="22">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C115" s="23">
@@ -6553,21 +8552,37 @@
         <v/>
       </c>
       <c r="D115" s="22">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E115" s="24">
         <f>IF(OR(D115="",D115=-999),"",D115+$E$2)</f>
         <v/>
       </c>
+      <c r="F115" s="22">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G115" s="24">
+        <f>IF(OR(F115="",F115=-999),"",F115+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H115" s="22">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I115" s="24">
+        <f>IF(OR(H115="",H115=-999),"",H115+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="116" ht="15" customHeight="1">
       <c r="A116" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B116" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C116" s="27">
@@ -6575,21 +8590,37 @@
         <v/>
       </c>
       <c r="D116" s="26">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E116" s="28">
         <f>IF(OR(D116="",D116=-999),"",D116+$E$2)</f>
         <v/>
       </c>
+      <c r="F116" s="26">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G116" s="28">
+        <f>IF(OR(F116="",F116=-999),"",F116+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H116" s="26">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I116" s="28">
+        <f>IF(OR(H116="",H116=-999),"",H116+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="117" ht="15" customHeight="1">
       <c r="A117" s="21">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B117" s="22">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C117" s="23">
@@ -6597,21 +8628,37 @@
         <v/>
       </c>
       <c r="D117" s="22">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E117" s="24">
         <f>IF(OR(D117="",D117=-999),"",D117+$E$2)</f>
         <v/>
       </c>
+      <c r="F117" s="22">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G117" s="24">
+        <f>IF(OR(F117="",F117=-999),"",F117+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H117" s="22">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I117" s="24">
+        <f>IF(OR(H117="",H117=-999),"",H117+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="118" ht="15" customHeight="1">
       <c r="A118" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B118" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C118" s="27">
@@ -6619,21 +8666,37 @@
         <v/>
       </c>
       <c r="D118" s="26">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E118" s="28">
         <f>IF(OR(D118="",D118=-999),"",D118+$E$2)</f>
         <v/>
       </c>
+      <c r="F118" s="26">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G118" s="28">
+        <f>IF(OR(F118="",F118=-999),"",F118+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H118" s="26">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I118" s="28">
+        <f>IF(OR(H118="",H118=-999),"",H118+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="119" ht="15" customHeight="1">
       <c r="A119" s="21">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B119" s="22">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C119" s="23">
@@ -6641,21 +8704,37 @@
         <v/>
       </c>
       <c r="D119" s="22">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E119" s="24">
         <f>IF(OR(D119="",D119=-999),"",D119+$E$2)</f>
         <v/>
       </c>
+      <c r="F119" s="22">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G119" s="24">
+        <f>IF(OR(F119="",F119=-999),"",F119+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H119" s="22">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I119" s="24">
+        <f>IF(OR(H119="",H119=-999),"",H119+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="120" ht="15" customHeight="1">
       <c r="A120" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B120" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C120" s="27">
@@ -6663,21 +8742,37 @@
         <v/>
       </c>
       <c r="D120" s="26">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E120" s="28">
         <f>IF(OR(D120="",D120=-999),"",D120+$E$2)</f>
         <v/>
       </c>
+      <c r="F120" s="26">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G120" s="28">
+        <f>IF(OR(F120="",F120=-999),"",F120+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H120" s="26">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I120" s="28">
+        <f>IF(OR(H120="",H120=-999),"",H120+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="121" ht="15" customHeight="1">
       <c r="A121" s="21">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B121" s="22">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C121" s="23">
@@ -6685,21 +8780,37 @@
         <v/>
       </c>
       <c r="D121" s="22">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E121" s="24">
         <f>IF(OR(D121="",D121=-999),"",D121+$E$2)</f>
         <v/>
       </c>
+      <c r="F121" s="22">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G121" s="24">
+        <f>IF(OR(F121="",F121=-999),"",F121+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H121" s="22">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I121" s="24">
+        <f>IF(OR(H121="",H121=-999),"",H121+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="122" ht="15" customHeight="1">
       <c r="A122" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B122" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C122" s="27">
@@ -6707,21 +8818,37 @@
         <v/>
       </c>
       <c r="D122" s="26">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E122" s="28">
         <f>IF(OR(D122="",D122=-999),"",D122+$E$2)</f>
         <v/>
       </c>
+      <c r="F122" s="26">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G122" s="28">
+        <f>IF(OR(F122="",F122=-999),"",F122+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H122" s="26">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I122" s="28">
+        <f>IF(OR(H122="",H122=-999),"",H122+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="123" ht="15" customHeight="1">
       <c r="A123" s="21">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B123" s="22">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C123" s="23">
@@ -6729,21 +8856,37 @@
         <v/>
       </c>
       <c r="D123" s="22">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E123" s="24">
         <f>IF(OR(D123="",D123=-999),"",D123+$E$2)</f>
         <v/>
       </c>
+      <c r="F123" s="22">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G123" s="24">
+        <f>IF(OR(F123="",F123=-999),"",F123+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H123" s="22">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I123" s="24">
+        <f>IF(OR(H123="",H123=-999),"",H123+$E$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="124" ht="15" customHeight="1">
       <c r="A124" s="25">
-        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-23)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-23)),"")</f>
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
         <v/>
       </c>
       <c r="B124" s="26">
-        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-23,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="C124" s="27">
@@ -6751,60 +8894,152 @@
         <v/>
       </c>
       <c r="D124" s="26">
-        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-23,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
         <v/>
       </c>
       <c r="E124" s="28">
         <f>IF(OR(D124="",D124=-999),"",D124+$E$2)</f>
         <v/>
       </c>
-    </row>
-    <row r="125" ht="24" customHeight="1">
-      <c r="A125" s="5" t="inlineStr">
-        <is>
-          <t>↑ Formulas cover 100 rows. For more data: select A25:E124 and copy-paste downward. For very large datasets use Power Query — see Instructions sheet.</t>
+      <c r="F124" s="26">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G124" s="28">
+        <f>IF(OR(F124="",F124=-999),"",F124+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H124" s="26">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I124" s="28">
+        <f>IF(OR(H124="",H124=-999),"",H124+$E$2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125" ht="15" customHeight="1">
+      <c r="A125" s="21">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
+        <v/>
+      </c>
+      <c r="B125" s="22">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C125" s="23">
+        <f>IF(OR(B125="",B125=-999),"",B125*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D125" s="22">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E125" s="24">
+        <f>IF(OR(D125="",D125=-999),"",D125+$E$2)</f>
+        <v/>
+      </c>
+      <c r="F125" s="22">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G125" s="24">
+        <f>IF(OR(F125="",F125=-999),"",F125+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H125" s="22">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I125" s="24">
+        <f>IF(OR(H125="",H125=-999),"",H125+$E$2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="126" ht="15" customHeight="1">
+      <c r="A126" s="25">
+        <f>IFERROR(IF(INDEX('Raw Flow Data'!$A:$A,ROW()-25)="","",INDEX('Raw Flow Data'!$A:$A,ROW()-25)),"")</f>
+        <v/>
+      </c>
+      <c r="B126" s="26">
+        <f>IFERROR(IF($B$3="","",INDEX('Raw Flow Data'!$A:$ZZ,ROW()-25,MATCH($B$3,'Raw Flow Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C126" s="27">
+        <f>IF(OR(B126="",B126=-999),"",B126*$B$2)</f>
+        <v/>
+      </c>
+      <c r="D126" s="26">
+        <f>IFERROR(IF($E$3="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$3,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E126" s="28">
+        <f>IF(OR(D126="",D126=-999),"",D126+$E$2)</f>
+        <v/>
+      </c>
+      <c r="F126" s="26">
+        <f>IFERROR(IF($E$4="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$4,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="G126" s="28">
+        <f>IF(OR(F126="",F126=-999),"",F126+$E$2)</f>
+        <v/>
+      </c>
+      <c r="H126" s="26">
+        <f>IFERROR(IF($E$5="","",INDEX('Raw Pressure Data'!$A:$ZZ,ROW()-25,MATCH($E$5,'Raw Pressure Data'!$1:$1,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I126" s="28">
+        <f>IF(OR(H126="",H126=-999),"",H126+$E$2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="127" ht="24" customHeight="1">
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>↑ Formulas cover 100 rows (A27:I126). For more data: select that range and copy-paste downward.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="38">
     <mergeCell ref="D20:E20"/>
+    <mergeCell ref="A25:I25"/>
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="A11:B11"/>
+    <mergeCell ref="D22:E22"/>
     <mergeCell ref="A6:B6"/>
+    <mergeCell ref="D21:E21"/>
     <mergeCell ref="D6:E6"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="D11:E11"/>
     <mergeCell ref="D13:E13"/>
+    <mergeCell ref="A23:I23"/>
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="D17:E17"/>
     <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A21:E21"/>
     <mergeCell ref="D16:E16"/>
     <mergeCell ref="D7:E7"/>
     <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A127:I127"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="D18:E18"/>
     <mergeCell ref="A17:B17"/>
-    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="A8:B8"/>
     <mergeCell ref="D9:E9"/>
-    <mergeCell ref="A8:B8"/>
     <mergeCell ref="D12:E12"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="D8:E8"/>
     <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A125:E125"/>
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="D5:E5"/>
     <mergeCell ref="A10:B10"/>
+    <mergeCell ref="D14:E14"/>
     <mergeCell ref="A13:B13"/>
-    <mergeCell ref="D14:E14"/>
     <mergeCell ref="A9:B9"/>
   </mergeCells>
   <conditionalFormatting sqref="A5:B20">
@@ -6812,16 +9047,22 @@
       <formula>$A5=$B$3</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D5:E20">
+  <conditionalFormatting sqref="D7:E22">
     <cfRule type="expression" priority="2" dxfId="1">
-      <formula>$D5=$E$3</formula>
+      <formula>OR($D7=$E$3,$D7=$E$4,$D7=$E$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="2">
-    <dataValidation sqref="B3" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Unknown Flow" error="Select a name from the Raw Flow Data headers." type="list">
+  <dataValidations count="4">
+    <dataValidation sqref="B3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Raw Flow Data'!$B$1:$GR$1</formula1>
     </dataValidation>
-    <dataValidation sqref="E3" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Unknown Pressure" error="Select a name from the Raw Pressure Data headers." type="list">
+    <dataValidation sqref="E3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Raw Pressure Data'!$B$1:$GR$1</formula1>
+    </dataValidation>
+    <dataValidation sqref="E4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Raw Pressure Data'!$B$1:$GR$1</formula1>
+    </dataValidation>
+    <dataValidation sqref="E5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Raw Pressure Data'!$B$1:$GR$1</formula1>
     </dataValidation>
   </dataValidations>
@@ -6928,7 +9169,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A65"/>
+  <dimension ref="A1:A69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="115" customWidth="1" min="1" max="1"/>
@@ -6973,274 +9214,282 @@
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="30" t="inlineStr">
         <is>
-          <t>Step 4:  Use the 'Select Flow ▼' dropdown (cell B3) to pick a flow.</t>
+          <t>Step 4:  Use 'Pressure 1 ▼' (cell E3) to pick the first pressure to display.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">         The selected flow is highlighted in the list on the left.</t>
+          <t xml:space="preserve">         Optionally use 'Pressure 2 ▼' (E4) and 'Pressure 3 ▼' (E5) for more series.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="30" t="inlineStr">
         <is>
-          <t>Step 5:  Use the 'Select Pressure ▼' dropdown (cell E3) to pick a pressure.</t>
+          <t xml:space="preserve">         Leave E4 / E5 blank to show fewer than 3 pressure lines on the chart.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">         The selected pressure is highlighted in the list on the right.</t>
+          <t>Step 5:  Use 'Select Flow ▼' (cell B3) to pick a flow.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="30" t="inlineStr">
         <is>
-          <t>Step 6:  Adjust 'Flow Scaling Factor' (B2) and 'Pressure Offset' (E2) if needed.</t>
+          <t xml:space="preserve">         Leave B3 blank to hide the Flow line and show only pressure(s).</t>
         </is>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="30" t="inlineStr">
         <is>
-          <t>Step 7:  The chart (right side) and formula table (below) update instantly.</t>
+          <t>Step 6:  Adjust 'Flow Scaling Factor' (B2) and 'Pressure Offset' (E2) if needed.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="30" t="inlineStr">
         <is>
+          <t>Step 7:  The chart (right side) and formula table (below) update instantly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="30" t="inlineStr">
+        <is>
           <t>Step 8:  When satisfied, run the SaveToMOD macro to store the adjusted data.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="30" t="inlineStr"/>
-    </row>
     <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="30" t="inlineStr">
-        <is>
-          <t>NOTE:  After pasting your own data, right-click cell B3 → Data Validation → update</t>
-        </is>
-      </c>
+      <c r="A15" s="30" t="inlineStr"/>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">       Source to cover your column range, e.g.  'Raw Flow Data'!$B$1:$BZ$1</t>
+          <t>NOTE:  After pasting your own data, right-click each selector cell (B3, E3-E5)</t>
         </is>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
       <c r="A17" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">       Do the same for E3 using 'Raw Pressure Data'.</t>
+          <t xml:space="preserve">       → Data Validation → update the Source to cover your column range,</t>
         </is>
       </c>
     </row>
     <row r="18" ht="17" customHeight="1">
-      <c r="A18" s="30" t="inlineStr"/>
+      <c r="A18" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       e.g.  'Raw Flow Data'!$B$1:$BZ$1</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="17" customHeight="1">
-      <c r="A19" s="30" t="inlineStr">
-        <is>
-          <t>NOTE:  The formula table covers 100 rows. For longer datasets, select A25:E124</t>
-        </is>
-      </c>
+      <c r="A19" s="30" t="inlineStr"/>
     </row>
     <row r="20" ht="17" customHeight="1">
       <c r="A20" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">       and copy-paste downward as far as needed.</t>
+          <t>NOTE:  The formula table covers 100 rows (A27:I126). For longer datasets, select</t>
         </is>
       </c>
     </row>
     <row r="21" ht="17" customHeight="1">
-      <c r="A21" s="30" t="inlineStr"/>
+      <c r="A21" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       that range and copy-paste downward as far as needed.</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="17" customHeight="1">
-      <c r="A22" s="30" t="inlineStr">
+      <c r="A22" s="30" t="inlineStr"/>
+    </row>
+    <row r="23" ht="17" customHeight="1">
+      <c r="A23" s="30" t="inlineStr">
         <is>
           <t>NOTE:  -999 values are treated as no-data and are excluded from all calculations.</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="8" customHeight="1"/>
-    <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="31" t="inlineStr">
+    <row r="24" ht="8" customHeight="1"/>
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="31" t="inlineStr">
         <is>
           <t>2.  POWER QUERY SETUP  (optional — recommended for very large datasets)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="17" customHeight="1">
-      <c r="A25" s="30" t="inlineStr">
-        <is>
-          <t>The Raw data sheets are already set up as Excel Tables (FlowData, PressureData).</t>
         </is>
       </c>
     </row>
     <row r="26" ht="17" customHeight="1">
       <c r="A26" s="30" t="inlineStr">
         <is>
+          <t>The Raw data sheets are already set up as Excel Tables (FlowData, PressureData).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="17" customHeight="1">
+      <c r="A27" s="30" t="inlineStr">
+        <is>
           <t>Power Query can load these tables, unpivot them, and merge them for use in PivotTables.</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="17" customHeight="1">
-      <c r="A27" s="30" t="inlineStr"/>
-    </row>
     <row r="28" ht="17" customHeight="1">
-      <c r="A28" s="30" t="inlineStr">
-        <is>
-          <t>Step 1:  Data tab → Get Data → From Table/Range → select the FlowData table.</t>
-        </is>
-      </c>
+      <c r="A28" s="30" t="inlineStr"/>
     </row>
     <row r="29" ht="17" customHeight="1">
       <c r="A29" s="30" t="inlineStr">
         <is>
-          <t>Step 2:  In Power Query Editor: select the Date column, then Home → Unpivot Other Columns.</t>
+          <t>Step 1:  Data tab → Get Data → From Table/Range → select the FlowData table.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="17" customHeight="1">
       <c r="A30" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">         Rename 'Attribute' → 'Flow Name',  'Value' → 'Flow Value'.</t>
+          <t>Step 2:  In Power Query Editor: select the Date column, then Home → Unpivot Other Columns.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="17" customHeight="1">
       <c r="A31" s="30" t="inlineStr">
         <is>
-          <t>Step 3:  Close &amp; Load To… → Only Create Connection.  Name the query  FlowLong.</t>
+          <t xml:space="preserve">         Rename 'Attribute' → 'Flow Name',  'Value' → 'Flow Value'.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="17" customHeight="1">
       <c r="A32" s="30" t="inlineStr">
         <is>
-          <t>Step 4:  Repeat for PressureData.  Name the query  PressureLong.</t>
+          <t>Step 3:  Close &amp; Load To… → Only Create Connection.  Name the query  FlowLong.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="17" customHeight="1">
       <c r="A33" s="30" t="inlineStr">
         <is>
-          <t>Step 5:  Merge the two queries on Date + Name to get a combined table.</t>
+          <t>Step 4:  Repeat for PressureData.  Name the query  PressureLong.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="17" customHeight="1">
       <c r="A34" s="30" t="inlineStr">
         <is>
-          <t>Step 6:  Add calculated columns:  Flow Adjusted = [Flow Value] × scaling_factor</t>
+          <t>Step 5:  Merge the two queries on Date + Name to get a combined table.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="17" customHeight="1">
       <c r="A35" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Pressure Adjusted = [Pressure Value] + offset</t>
+          <t>Step 6:  Add calculated columns:  Flow Adjusted = [Flow Value] × scaling_factor</t>
         </is>
       </c>
     </row>
     <row r="36" ht="17" customHeight="1">
       <c r="A36" s="30" t="inlineStr">
         <is>
+          <t xml:space="preserve">                                  Pressure Adjusted = [Pressure Value] + offset</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="17" customHeight="1">
+      <c r="A37" s="30" t="inlineStr">
+        <is>
           <t>Step 7:  Load the merged query to a sheet and build a PivotTable + Slicer on top of it.</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="17" customHeight="1">
-      <c r="A37" s="30" t="inlineStr"/>
-    </row>
     <row r="38" ht="17" customHeight="1">
-      <c r="A38" s="30" t="inlineStr">
+      <c r="A38" s="30" t="inlineStr"/>
+    </row>
+    <row r="39" ht="17" customHeight="1">
+      <c r="A39" s="30" t="inlineStr">
         <is>
           <t>After pasting new data:  Data tab → Refresh All  (Ctrl+Alt+F5).</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="8" customHeight="1"/>
-    <row r="40" ht="26" customHeight="1">
-      <c r="A40" s="32" t="inlineStr">
+    <row r="40" ht="8" customHeight="1"/>
+    <row r="41" ht="26" customHeight="1">
+      <c r="A41" s="32" t="inlineStr">
         <is>
           <t>3.  PIVOTTABLE + SLICER  (optional — for interactive multi-flow comparison)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="17" customHeight="1">
-      <c r="A41" s="30" t="inlineStr">
-        <is>
-          <t>Once the Power Query merged table is loaded to a sheet:</t>
         </is>
       </c>
     </row>
     <row r="42" ht="17" customHeight="1">
       <c r="A42" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Insert → PivotTable</t>
+          <t>Once the Power Query merged table is loaded to a sheet:</t>
         </is>
       </c>
     </row>
     <row r="43" ht="17" customHeight="1">
       <c r="A43" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Rows: Date    Values: Flow Adjusted, Pressure Adjusted</t>
+          <t xml:space="preserve">  • Insert → PivotTable</t>
         </is>
       </c>
     </row>
     <row r="44" ht="17" customHeight="1">
       <c r="A44" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • PivotTable Analyze → Insert Slicer → tick 'Flow Name' → OK</t>
+          <t xml:space="preserve">  • Rows: Date    Values: Flow Adjusted, Pressure Adjusted</t>
         </is>
       </c>
     </row>
     <row r="45" ht="17" customHeight="1">
       <c r="A45" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Click a flow name in the Slicer to filter instantly</t>
+          <t xml:space="preserve">  • PivotTable Analyze → Insert Slicer → tick 'Flow Name' → OK</t>
         </is>
       </c>
     </row>
     <row r="46" ht="17" customHeight="1">
       <c r="A46" s="30" t="inlineStr">
         <is>
+          <t xml:space="preserve">  • Click a flow name in the Slicer to filter instantly</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="17" customHeight="1">
+      <c r="A47" s="30" t="inlineStr">
+        <is>
           <t xml:space="preserve">  • Insert → PivotChart → Line → add Secondary Axis to the Pressure series</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="8" customHeight="1"/>
-    <row r="48" ht="26" customHeight="1">
-      <c r="A48" s="33" t="inlineStr">
+    <row r="48" ht="8" customHeight="1"/>
+    <row r="49" ht="26" customHeight="1">
+      <c r="A49" s="33" t="inlineStr">
         <is>
           <t>4.  VBA SAVE BUTTON  (paste this into a Module — Alt+F11 → Insert → Module)</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="17" customHeight="1">
-      <c r="A49" s="34" t="inlineStr">
+    <row r="50" ht="17" customHeight="1">
+      <c r="A50" s="34" t="inlineStr">
         <is>
           <t>Assign the macro to a button on the Dashboard: Developer tab → Insert → Button (Form Control).</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="8" customHeight="1"/>
-    <row r="51" ht="17" customHeight="1">
-      <c r="A51" s="35" t="inlineStr">
+    <row r="51" ht="8" customHeight="1"/>
+    <row r="52" ht="17" customHeight="1">
+      <c r="A52" s="35" t="inlineStr">
         <is>
           <t>' ═══════════════════════════════════════════════════════════════════════════
 ' SaveToMOD  —  appends current adjusted data to MOD Flow and MOD Pressure
-' Reads:  B3 (selected flow), E3 (selected pressure), B2 (scaling), E2 (offset)
-'         Data table rows 25 onwards, columns A-E
+' Reads:  B3 (selected flow), E3 (pressure 1), B2 (scaling), E2 (offset)
+'         Data table rows 27+, col C = Flow Adjusted, col E = Pressure 1 Adjusted
+'         (Pressure 2/3 in cols G/I are not saved by this macro — extend as needed)
 ' ═══════════════════════════════════════════════════════════════════════════
 Sub SaveToMOD()
     Dim wsDash    As Worksheet
@@ -7272,11 +9521,11 @@
         Exit Sub
     End If
     ' ── Find last row with data ──────────────────────────────────────────────
-    Const DATA_START As Long = 25
+    Const DATA_START As Long = 27
     Dim lastRow As Long
     lastRow = wsDash.Cells(wsDash.Rows.Count, "A").End(xlUp).Row
     If lastRow &lt; DATA_START Then
-        MsgBox "No data found in the formula table (rows 25 onwards).", _
+        MsgBox "No data found in the formula table (rows 27 onwards).", _
                vbExclamation, "No Data"
         Exit Sub
     End If
@@ -7296,7 +9545,7 @@
         Dim presAdj   As Variant
         dtVal   = wsDash.Cells(i, "A").Value   ' Date
         flowAdj = wsDash.Cells(i, "C").Value   ' Flow Adjusted   (col C)
-        presAdj = wsDash.Cells(i, "E").Value   ' Pressure Adjusted (col E)
+        presAdj = wsDash.Cells(i, "E").Value   ' Pressure 1 Adjusted (col E)
         If dtVal = "" Then GoTo Skip
         If flowAdj &lt;&gt; "" Then
             wsModFlow.Cells(nFlow, "A").Value         = dtVal
@@ -7331,87 +9580,108 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="8" customHeight="1"/>
-    <row r="53" ht="26" customHeight="1">
-      <c r="A53" s="36" t="inlineStr">
+    <row r="53" ht="8" customHeight="1"/>
+    <row r="54" ht="26" customHeight="1">
+      <c r="A54" s="36" t="inlineStr">
         <is>
           <t>5.  DATA FORMAT REFERENCE</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="17" customHeight="1">
-      <c r="A54" s="30" t="inlineStr">
+    <row r="55" ht="17" customHeight="1">
+      <c r="A55" s="30" t="inlineStr">
         <is>
           <t>Both Raw Data sheets expect this wide format:</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="17" customHeight="1">
-      <c r="A55" s="30" t="inlineStr"/>
-    </row>
     <row r="56" ht="17" customHeight="1">
-      <c r="A56" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Date               | AL012       | AL013       | AL014       | ...  </t>
-        </is>
-      </c>
+      <c r="A56" s="30" t="inlineStr"/>
     </row>
     <row r="57" ht="17" customHeight="1">
       <c r="A57" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">    12/01/2026 00:00   | 3.168205    | 2.204250    | 2.665153    | ...  </t>
+          <t xml:space="preserve">    Date               | AL012       | AL013       | AL014       | ...  </t>
         </is>
       </c>
     </row>
     <row r="58" ht="17" customHeight="1">
       <c r="A58" s="30" t="inlineStr">
         <is>
+          <t xml:space="preserve">    12/01/2026 00:00   | 3.168205    | 2.204250    | 2.665153    | ...  </t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="17" customHeight="1">
+      <c r="A59" s="30" t="inlineStr">
+        <is>
           <t xml:space="preserve">    12/01/2026 00:15   | 3.190769    | 2.225250    | 2.681334    | ...  </t>
         </is>
       </c>
     </row>
-    <row r="59" ht="17" customHeight="1">
-      <c r="A59" s="30" t="inlineStr"/>
-    </row>
     <row r="60" ht="17" customHeight="1">
-      <c r="A60" s="30" t="inlineStr">
-        <is>
-          <t>• Column A must contain a proper Date/Time value (not text).</t>
-        </is>
-      </c>
+      <c r="A60" s="30" t="inlineStr"/>
     </row>
     <row r="61" ht="17" customHeight="1">
       <c r="A61" s="30" t="inlineStr">
         <is>
-          <t>• Flow and pressure column names can be any mix of letters and numbers.</t>
+          <t>• Column A must contain a proper Date/Time value (not text).</t>
         </is>
       </c>
     </row>
     <row r="62" ht="17" customHeight="1">
       <c r="A62" s="30" t="inlineStr">
         <is>
-          <t>• The flow names in Raw Flow Data and the pressure names in Raw Pressure Data</t>
+          <t>• Flow and pressure column names can be any mix of letters and numbers.</t>
         </is>
       </c>
     </row>
     <row r="63" ht="17" customHeight="1">
       <c r="A63" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">  do NOT need to match — you select each independently on the Dashboard.</t>
+          <t>• The flow names in Raw Flow Data and the pressure names in Raw Pressure Data</t>
         </is>
       </c>
     </row>
     <row r="64" ht="17" customHeight="1">
       <c r="A64" s="30" t="inlineStr">
         <is>
-          <t>• Use -999 for missing/no-data values — they are excluded from all calculations.</t>
+          <t xml:space="preserve">  do NOT need to match — you select each independently on the Dashboard.</t>
         </is>
       </c>
     </row>
     <row r="65" ht="17" customHeight="1">
       <c r="A65" s="30" t="inlineStr">
         <is>
+          <t>• Use -999 for missing/no-data values — they are excluded from all calculations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="17" customHeight="1">
+      <c r="A66" s="30" t="inlineStr">
+        <is>
           <t>• Data can be any length: months of 15-minute data = thousands of rows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="17" customHeight="1">
+      <c r="A67" s="30" t="inlineStr">
+        <is>
+          <t>• Columns F/G = Pressure 2 Raw/Adjusted  (driven by E4),</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="17" customHeight="1">
+      <c r="A68" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Columns H/I = Pressure 3 Raw/Adjusted  (driven by E5).</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="17" customHeight="1">
+      <c r="A69" s="30" t="inlineStr">
+        <is>
+          <t>• Leave E4 or E5 blank to leave those columns empty (no performance impact).</t>
         </is>
       </c>
     </row>

--- a/Flow_Pressure_Dashboard.xlsx
+++ b/Flow_Pressure_Dashboard.xlsx
@@ -1219,30 +1219,33 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="7200000" cy="5040000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="7200000" cy="5040000"/>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Flow_Pressure_Dashboard.xlsx
+++ b/Flow_Pressure_Dashboard.xlsx
@@ -1605,30 +1605,40 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="7200000" cy="5040000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>799200</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>112400</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks noGrp="1"/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Flow_Pressure_Dashboard.xlsx
+++ b/Flow_Pressure_Dashboard.xlsx
@@ -738,9 +738,6 @@
           </c:val>
           <c:smooth val="0"/>
         </c:ser>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
         <c:smooth val="0"/>
         <c:axId val="1001"/>
         <c:axId val="1002"/>
@@ -1508,9 +1505,6 @@
           </c:val>
           <c:smooth val="0"/>
         </c:ser>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
         <c:smooth val="0"/>
         <c:axId val="1001"/>
         <c:axId val="1003"/>
